--- a/Data Set/Teamsync_new_testcases.xlsx
+++ b/Data Set/Teamsync_new_testcases.xlsx
@@ -405,7 +405,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -692,6 +692,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6346,7 +6350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="17.08984375" bestFit="1" customWidth="1" style="29" min="1" max="1"/>
@@ -6441,6 +6445,8 @@
       </c>
       <c r="B7" s="49" t="n"/>
     </row>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10" ht="31" customHeight="1" s="29">
       <c r="A10" s="54" t="inlineStr">
         <is>
@@ -6568,9 +6574,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K12" s="41" t="inlineStr">
+      <c r="K12" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L12" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M12" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:49:30 (0.26s)</t>
         </is>
       </c>
     </row>
@@ -6617,9 +6633,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K13" s="41" t="inlineStr">
+      <c r="K13" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L13" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M13" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:49:30 (0.19s)</t>
         </is>
       </c>
     </row>
@@ -6666,9 +6692,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K14" s="41" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="K14" s="106" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="L14" s="107" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request | AssertionError: [API] Expected 200, got 400</t>
+        </is>
+      </c>
+      <c r="M14" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:49:30 (0.26s)</t>
         </is>
       </c>
     </row>
@@ -6715,9 +6751,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K15" s="41" t="inlineStr">
+      <c r="K15" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L15" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M15" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:49:31 (0.31s)</t>
         </is>
       </c>
     </row>
@@ -6764,9 +6810,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K16" s="41" t="inlineStr">
+      <c r="K16" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L16" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M16" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:49:33 (2.76s)</t>
         </is>
       </c>
     </row>
@@ -6813,9 +6869,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K17" s="41" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="K17" s="104" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L17" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request</t>
+        </is>
+      </c>
+      <c r="M17" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:49:34 (0.50s)</t>
         </is>
       </c>
     </row>
@@ -6862,9 +6928,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K18" s="41" t="inlineStr">
+      <c r="K18" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L18" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M18" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:49:37 (3.29s)</t>
         </is>
       </c>
     </row>
@@ -6911,9 +6987,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K19" s="41" t="inlineStr">
+      <c r="K19" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L19" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M19" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:49:42 (4.42s)</t>
         </is>
       </c>
     </row>
@@ -6960,9 +7046,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K20" s="41" t="inlineStr">
+      <c r="K20" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L20" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 0</t>
+        </is>
+      </c>
+      <c r="M20" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:49:47 (5.79s)</t>
         </is>
       </c>
     </row>
@@ -7009,9 +7105,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K21" s="41" t="inlineStr">
+      <c r="K21" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L21" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M21" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:49:53 (5.31s)</t>
         </is>
       </c>
     </row>
@@ -7058,9 +7164,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K22" s="41" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="K22" s="104" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L22" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 404 Not Found</t>
+        </is>
+      </c>
+      <c r="M22" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:49:53 (0.16s)</t>
         </is>
       </c>
     </row>
@@ -7107,9 +7223,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K23" s="41" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="K23" s="106" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="L23" s="107" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request | AssertionError: [API] Bulk move failed: 400</t>
+        </is>
+      </c>
+      <c r="M23" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:49:53 (0.32s)</t>
         </is>
       </c>
     </row>
@@ -7156,9 +7282,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K24" s="41" t="inlineStr">
+      <c r="K24" s="104" t="inlineStr">
         <is>
           <t>Pass</t>
+        </is>
+      </c>
+      <c r="L24" s="105" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M24" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:49:56 (2.68s)</t>
         </is>
       </c>
     </row>
@@ -7214,6 +7350,8 @@
       <c r="J28" s="11" t="n"/>
       <c r="K28" s="11" t="n"/>
     </row>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31" ht="31" customHeight="1" s="29">
       <c r="A31" s="51" t="inlineStr">
         <is>
@@ -7236,6 +7374,9 @@
           <t>Total Test Cases</t>
         </is>
       </c>
+      <c r="K31" s="76" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="32" ht="31" customHeight="1" s="29">
       <c r="B32" s="51" t="inlineStr">
@@ -7249,7 +7390,9 @@
           <t>Executed Test Cases</t>
         </is>
       </c>
-      <c r="K32" s="53" t="n"/>
+      <c r="K32" s="77" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="33" ht="31" customHeight="1" s="29">
       <c r="B33" s="51" t="inlineStr">
@@ -7263,7 +7406,9 @@
           <t>Passed Test Cases</t>
         </is>
       </c>
-      <c r="K33" s="53" t="n"/>
+      <c r="K33" s="77" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="34" ht="31" customHeight="1" s="29">
       <c r="B34" s="51" t="inlineStr">
@@ -7277,7 +7422,9 @@
           <t>Failed Test Cases</t>
         </is>
       </c>
-      <c r="K34" s="53" t="n"/>
+      <c r="K34" s="77" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="35" ht="31" customHeight="1" s="29">
       <c r="B35" s="51" t="inlineStr">
@@ -7291,7 +7438,9 @@
           <t>Blocked Test Cases</t>
         </is>
       </c>
-      <c r="K35" s="53" t="n"/>
+      <c r="K35" s="77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" ht="46.5" customHeight="1" s="29">
       <c r="B36" s="51" t="inlineStr">
@@ -7305,8 +7454,14 @@
           <t>Not Executed Test Cases</t>
         </is>
       </c>
-      <c r="K36" s="53" t="n"/>
-    </row>
+      <c r="K36" s="77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10365,7 +10520,7 @@
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:31:13 (4.74s)</t>
+          <t>2026-05-25 15:29:37 (2.07s)</t>
         </is>
       </c>
     </row>
@@ -10424,7 +10579,7 @@
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:31:16 (1.05s)</t>
+          <t>2026-05-25 15:29:40 (1.17s)</t>
         </is>
       </c>
     </row>
@@ -10483,7 +10638,7 @@
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:31:19 (0.93s)</t>
+          <t>2026-05-25 15:29:52 (6.17s)</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10697,7 @@
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:31:20 (0.00s)</t>
+          <t>2026-05-25 15:29:55 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10756,7 @@
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:31:22 (2.60s)</t>
+          <t>2026-05-25 15:30:06 (10.20s)</t>
         </is>
       </c>
     </row>
@@ -10648,19 +10803,19 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="K19" s="92" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="L19" s="93" t="inlineStr">
-        <is>
-          <t>HTTP 401 Unauthorized</t>
+      <c r="K19" s="97" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="L19" s="101" t="inlineStr">
+        <is>
+          <t>HTTP 500 Internal Server Error | AssertionError: [API] Expected 401, got 500. Body: {"error":"Incorrect credentials","message":""}</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:31:36 (3.79s)</t>
+          <t>2026-05-25 15:30:16 (0.12s)</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10874,7 @@
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:31:40 (3.77s)</t>
+          <t>2026-05-25 15:30:25 (8.62s)</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10933,7 @@
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:31:43 (2.59s)</t>
+          <t>2026-05-25 15:30:33 (8.09s)</t>
         </is>
       </c>
     </row>
@@ -10825,19 +10980,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K22" s="92" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="L22" s="93" t="inlineStr">
-        <is>
-          <t>HTTP 401 Unauthorized</t>
+      <c r="K22" s="97" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="L22" s="101" t="inlineStr">
+        <is>
+          <t>HTTP 500 Internal Server Error | AssertionError: [API] Expected 400, got 500. Body: {"error":"Incorrect credentials","message":""}</t>
         </is>
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:31:45 (2.68s)</t>
+          <t>2026-05-25 15:30:33 (0.10s)</t>
         </is>
       </c>
     </row>
@@ -10896,7 +11051,7 @@
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:31:48 (2.63s)</t>
+          <t>2026-05-25 15:30:41 (7.89s)</t>
         </is>
       </c>
     </row>
@@ -10955,7 +11110,7 @@
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:31:51 (2.66s)</t>
+          <t>2026-05-25 15:30:49 (8.12s)</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11169,7 @@
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:31:51 (0.00s)</t>
+          <t>2026-05-25 15:30:49 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -11073,7 +11228,7 @@
       </c>
       <c r="M26" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:31:55 (3.86s)</t>
+          <t>2026-05-25 15:30:58 (9.05s)</t>
         </is>
       </c>
     </row>
@@ -11128,7 +11283,7 @@
       <c r="L27" s="93" t="inlineStr"/>
       <c r="M27" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:31:56 (0.41s)</t>
+          <t>2026-05-25 15:31:03 (0.43s)</t>
         </is>
       </c>
     </row>
@@ -11183,7 +11338,7 @@
       <c r="L28" s="93" t="inlineStr"/>
       <c r="M28" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:31:56 (0.37s)</t>
+          <t>2026-05-25 15:31:03 (0.26s)</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11393,7 @@
       <c r="L29" s="93" t="inlineStr"/>
       <c r="M29" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:31:56 (0.34s)</t>
+          <t>2026-05-25 15:31:03 (0.29s)</t>
         </is>
       </c>
     </row>
@@ -11293,7 +11448,7 @@
       <c r="L30" s="93" t="inlineStr"/>
       <c r="M30" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:31:57 (0.93s)</t>
+          <t>2026-05-25 15:31:06 (2.47s)</t>
         </is>
       </c>
     </row>
@@ -11340,19 +11495,19 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="K31" s="92" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="L31" s="93" t="inlineStr">
-        <is>
-          <t>HTTP 401 Unauthorized</t>
+      <c r="K31" s="97" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="L31" s="101" t="inlineStr">
+        <is>
+          <t>HTTP 500 Internal Server Error | AssertionError: [API] Expected 401, got 500. Body: {"error":"Incorrect credentials","message":""}</t>
         </is>
       </c>
       <c r="M31" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:32:01 (3.75s)</t>
+          <t>2026-05-25 15:31:06 (0.13s)</t>
         </is>
       </c>
     </row>
@@ -11411,7 +11566,7 @@
       </c>
       <c r="M32" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:32:02 (0.90s)</t>
+          <t>2026-05-25 15:31:12 (6.59s)</t>
         </is>
       </c>
     </row>
@@ -11478,7 +11633,7 @@
         </is>
       </c>
       <c r="K37" s="75" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" ht="29" customHeight="1" s="29">
@@ -11497,7 +11652,7 @@
         </is>
       </c>
       <c r="K38" s="75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" ht="29" customHeight="1" s="29">
@@ -11822,7 +11977,7 @@
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:32:23 (8.01s)</t>
+          <t>2026-05-25 15:31:43 (18.63s)</t>
         </is>
       </c>
       <c r="N12" s="11" t="n"/>
@@ -11887,7 +12042,7 @@
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:32:31 (8.41s)</t>
+          <t>2026-05-25 15:32:02 (18.21s)</t>
         </is>
       </c>
       <c r="N13" s="11" t="n"/>
@@ -11952,7 +12107,7 @@
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:32:40 (8.45s)</t>
+          <t>2026-05-25 15:32:20 (18.13s)</t>
         </is>
       </c>
       <c r="N14" s="11" t="n"/>
@@ -12017,7 +12172,7 @@
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:32:48 (7.87s)</t>
+          <t>2026-05-25 15:32:38 (18.14s)</t>
         </is>
       </c>
       <c r="N15" s="11" t="n"/>
@@ -12082,7 +12237,7 @@
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:32:56 (7.91s)</t>
+          <t>2026-05-25 15:32:56 (18.16s)</t>
         </is>
       </c>
       <c r="N16" s="11" t="n"/>
@@ -12142,7 +12297,7 @@
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:33:12 (16.87s)</t>
+          <t>2026-05-25 15:33:23 (27.15s)</t>
         </is>
       </c>
       <c r="N17" s="11" t="n"/>
@@ -12202,7 +12357,7 @@
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:34:45 (92.59s)</t>
+          <t>2026-05-25 15:34:46 (82.43s)</t>
         </is>
       </c>
       <c r="N18" s="11" t="n"/>
@@ -12250,19 +12405,19 @@
           <t>If 0 KB → "File is empty"</t>
         </is>
       </c>
-      <c r="K19" s="97" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="L19" s="98" t="inlineStr">
-        <is>
-          <t>AssertionError: [UI→API] test.docx upload — no upload response was captured</t>
+      <c r="K19" s="92" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L19" s="96" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:35:04 (18.38s)</t>
+          <t>2026-05-25 15:35:04 (18.06s)</t>
         </is>
       </c>
       <c r="N19" s="11" t="n"/>
@@ -12310,19 +12465,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K20" s="97" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="L20" s="98" t="inlineStr">
-        <is>
-          <t>HTTP 400 Bad Request | AssertionError: [UI→API] single file upload — expected 200, got 400</t>
+      <c r="K20" s="92" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L20" s="96" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:35:23 (18.71s)</t>
+          <t>2026-05-25 15:35:31 (27.12s)</t>
         </is>
       </c>
       <c r="N20" s="11" t="n"/>
@@ -12382,7 +12537,7 @@
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:36:42 (79.31s)</t>
+          <t>2026-05-25 15:35:58 (27.11s)</t>
         </is>
       </c>
       <c r="N21" s="11" t="n"/>
@@ -12442,7 +12597,7 @@
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:37:00 (17.87s)</t>
+          <t>2026-05-25 15:36:26 (27.22s)</t>
         </is>
       </c>
       <c r="N22" s="11" t="n"/>
@@ -12502,7 +12657,7 @@
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:37:17 (17.50s)</t>
+          <t>2026-05-25 15:36:55 (28.99s)</t>
         </is>
       </c>
       <c r="N23" s="11" t="n"/>
@@ -12562,7 +12717,7 @@
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:38:38 (80.44s)</t>
+          <t>2026-05-25 15:38:16 (81.45s)</t>
         </is>
       </c>
       <c r="N24" s="11" t="n"/>
@@ -12622,7 +12777,7 @@
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:38:56 (18.31s)</t>
+          <t>2026-05-25 15:38:34 (18.52s)</t>
         </is>
       </c>
       <c r="N25" s="11" t="n"/>
@@ -12682,7 +12837,7 @@
       </c>
       <c r="M26" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:39:14 (18.22s)</t>
+          <t>2026-05-25 15:38:53 (18.89s)</t>
         </is>
       </c>
       <c r="N26" s="11" t="n"/>
@@ -12742,7 +12897,7 @@
       </c>
       <c r="M27" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:40:50 (95.49s)</t>
+          <t>2026-05-25 15:40:16 (82.47s)</t>
         </is>
       </c>
       <c r="N27" s="11" t="n"/>
@@ -12802,7 +12957,7 @@
       </c>
       <c r="M28" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:40:57 (6.84s)</t>
+          <t>2026-05-25 15:40:21 (4.80s)</t>
         </is>
       </c>
       <c r="N28" s="11" t="n"/>
@@ -12862,7 +13017,7 @@
       </c>
       <c r="M29" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:40:58 (0.28s)</t>
+          <t>2026-05-25 15:40:21 (0.22s)</t>
         </is>
       </c>
       <c r="N29" s="11" t="n"/>
@@ -12918,7 +13073,7 @@
       <c r="L30" s="96" t="inlineStr"/>
       <c r="M30" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:41:29 (30.78s)</t>
+          <t>2026-05-25 15:40:34 (12.98s)</t>
         </is>
       </c>
       <c r="N30" s="11" t="n"/>
@@ -12978,7 +13133,7 @@
       </c>
       <c r="M31" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:43:01 (92.44s)</t>
+          <t>2026-05-25 15:41:56 (81.08s)</t>
         </is>
       </c>
       <c r="N31" s="11" t="n"/>
@@ -13038,7 +13193,7 @@
       </c>
       <c r="M32" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:43:01 (0.00s)</t>
+          <t>2026-05-25 15:41:56 (0.00s)</t>
         </is>
       </c>
       <c r="N32" s="11" t="n"/>
@@ -13086,19 +13241,19 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K33" s="97" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="L33" s="98" t="inlineStr">
-        <is>
-          <t>AssertionError: [UI→API] test.docx upload (precondition for download) — no upload response was captured</t>
+      <c r="K33" s="92" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L33" s="96" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M33" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:43:20 (18.36s)</t>
+          <t>2026-05-25 15:42:08 (12.36s)</t>
         </is>
       </c>
       <c r="N33" s="11" t="n"/>
@@ -13146,19 +13301,19 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K34" s="97" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="L34" s="98" t="inlineStr">
-        <is>
-          <t>HTTP 400 Bad Request | AssertionError: [UI→API] test.docx upload (precondition for delete) — expected 200, got 400</t>
+      <c r="K34" s="92" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L34" s="96" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M34" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:43:38 (18.70s)</t>
+          <t>2026-05-25 15:42:30 (21.73s)</t>
         </is>
       </c>
       <c r="N34" s="11" t="n"/>
@@ -13218,7 +13373,7 @@
       </c>
       <c r="M35" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:43:39 (0.18s)</t>
+          <t>2026-05-25 15:42:30 (0.06s)</t>
         </is>
       </c>
       <c r="N35" s="11" t="n"/>
@@ -13278,7 +13433,7 @@
       </c>
       <c r="M36" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:01 (81.95s)</t>
+          <t>2026-05-25 15:42:50 (20.08s)</t>
         </is>
       </c>
       <c r="N36" s="11" t="n"/>
@@ -13338,7 +13493,7 @@
       </c>
       <c r="M37" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:04 (3.15s)</t>
+          <t>2026-05-25 15:42:53 (2.48s)</t>
         </is>
       </c>
       <c r="N37" s="11" t="n"/>
@@ -13398,7 +13553,7 @@
       </c>
       <c r="M38" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:04 (0.16s)</t>
+          <t>2026-05-25 15:42:53 (0.18s)</t>
         </is>
       </c>
       <c r="N38" s="11" t="n"/>
@@ -13458,7 +13613,7 @@
       </c>
       <c r="M39" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:05 (0.20s)</t>
+          <t>2026-05-25 15:42:53 (0.16s)</t>
         </is>
       </c>
       <c r="N39" s="11" t="n"/>
@@ -13518,7 +13673,7 @@
       </c>
       <c r="M40" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:05 (0.16s)</t>
+          <t>2026-05-25 15:42:54 (0.16s)</t>
         </is>
       </c>
       <c r="N40" s="11" t="n"/>
@@ -13578,7 +13733,7 @@
       </c>
       <c r="M41" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:05 (0.28s)</t>
+          <t>2026-05-25 15:42:54 (0.16s)</t>
         </is>
       </c>
       <c r="N41" s="11" t="n"/>
@@ -13639,7 +13794,7 @@
       </c>
       <c r="M42" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:06 (0.22s)</t>
+          <t>2026-05-25 15:42:54 (0.19s)</t>
         </is>
       </c>
       <c r="N42" s="11" t="n"/>
@@ -13699,7 +13854,7 @@
       </c>
       <c r="M43" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:10 (3.73s)</t>
+          <t>2026-05-25 15:42:57 (2.59s)</t>
         </is>
       </c>
       <c r="N43" s="11" t="n"/>
@@ -13759,7 +13914,7 @@
       </c>
       <c r="M44" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:24 (14.32s)</t>
+          <t>2026-05-25 15:43:00 (2.46s)</t>
         </is>
       </c>
       <c r="N44" s="11" t="n"/>
@@ -13819,7 +13974,7 @@
       </c>
       <c r="M45" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:24 (0.00s)</t>
+          <t>2026-05-25 15:43:00 (0.00s)</t>
         </is>
       </c>
       <c r="N45" s="11" t="n"/>
@@ -13879,7 +14034,7 @@
       </c>
       <c r="M46" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:24 (0.00s)</t>
+          <t>2026-05-25 15:43:00 (0.00s)</t>
         </is>
       </c>
       <c r="N46" s="11" t="n"/>
@@ -13939,7 +14094,7 @@
       </c>
       <c r="M47" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:24 (0.00s)</t>
+          <t>2026-05-25 15:43:00 (0.00s)</t>
         </is>
       </c>
       <c r="N47" s="11" t="n"/>
@@ -13999,7 +14154,7 @@
       </c>
       <c r="M48" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:25 (0.53s)</t>
+          <t>2026-05-25 15:43:00 (0.33s)</t>
         </is>
       </c>
       <c r="N48" s="11" t="n"/>
@@ -14059,7 +14214,7 @@
       </c>
       <c r="M49" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:25 (0.00s)</t>
+          <t>2026-05-25 15:43:00 (0.00s)</t>
         </is>
       </c>
       <c r="N49" s="11" t="n"/>
@@ -14119,7 +14274,7 @@
       </c>
       <c r="M50" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:26 (0.20s)</t>
+          <t>2026-05-25 15:43:00 (0.15s)</t>
         </is>
       </c>
       <c r="N50" s="11" t="n"/>
@@ -14179,7 +14334,7 @@
       </c>
       <c r="M51" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:26 (0.69s)</t>
+          <t>2026-05-25 15:43:01 (0.35s)</t>
         </is>
       </c>
       <c r="N51" s="11" t="n"/>
@@ -14239,7 +14394,7 @@
       </c>
       <c r="M52" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:26 (0.00s)</t>
+          <t>2026-05-25 15:43:01 (0.00s)</t>
         </is>
       </c>
       <c r="N52" s="11" t="n"/>
@@ -14299,7 +14454,7 @@
       </c>
       <c r="M53" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:26 (0.00s)</t>
+          <t>2026-05-25 15:43:01 (0.00s)</t>
         </is>
       </c>
       <c r="N53" s="11" t="n"/>
@@ -14359,7 +14514,7 @@
       </c>
       <c r="M54" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:26 (0.00s)</t>
+          <t>2026-05-25 15:43:01 (0.00s)</t>
         </is>
       </c>
       <c r="N54" s="11" t="n"/>
@@ -14419,7 +14574,7 @@
       </c>
       <c r="M55" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:27 (0.17s)</t>
+          <t>2026-05-25 15:43:01 (0.18s)</t>
         </is>
       </c>
       <c r="N55" s="11" t="n"/>
@@ -14479,7 +14634,7 @@
       </c>
       <c r="M56" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:27 (0.00s)</t>
+          <t>2026-05-25 15:43:01 (0.00s)</t>
         </is>
       </c>
       <c r="N56" s="11" t="n"/>
@@ -14539,7 +14694,7 @@
       </c>
       <c r="M57" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:27 (0.00s)</t>
+          <t>2026-05-25 15:43:01 (0.00s)</t>
         </is>
       </c>
       <c r="N57" s="11" t="n"/>
@@ -14599,7 +14754,7 @@
       </c>
       <c r="M58" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:45:47 (20.01s)</t>
+          <t>2026-05-25 15:43:21 (19.83s)</t>
         </is>
       </c>
       <c r="N58" s="11" t="n"/>
@@ -14659,7 +14814,7 @@
       </c>
       <c r="M59" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:46:07 (19.94s)</t>
+          <t>2026-05-25 15:43:41 (19.85s)</t>
         </is>
       </c>
       <c r="N59" s="11" t="n"/>
@@ -14719,7 +14874,7 @@
       </c>
       <c r="M60" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:46:07 (0.00s)</t>
+          <t>2026-05-25 15:43:41 (0.00s)</t>
         </is>
       </c>
       <c r="N60" s="11" t="n"/>
@@ -14779,7 +14934,7 @@
       </c>
       <c r="M61" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:46:08 (0.65s)</t>
+          <t>2026-05-25 15:43:42 (0.39s)</t>
         </is>
       </c>
       <c r="N61" s="11" t="n"/>
@@ -14839,7 +14994,7 @@
       </c>
       <c r="M62" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:46:08 (0.51s)</t>
+          <t>2026-05-25 15:43:42 (0.35s)</t>
         </is>
       </c>
       <c r="N62" s="11" t="n"/>
@@ -14899,7 +15054,7 @@
       </c>
       <c r="M63" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:46:09 (0.25s)</t>
+          <t>2026-05-25 15:43:42 (0.17s)</t>
         </is>
       </c>
       <c r="N63" s="11" t="n"/>
@@ -14959,7 +15114,7 @@
       </c>
       <c r="M64" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:46:09 (0.41s)</t>
+          <t>2026-05-25 15:43:43 (0.37s)</t>
         </is>
       </c>
       <c r="N64" s="11" t="n"/>
@@ -15019,7 +15174,7 @@
       </c>
       <c r="M65" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:46:10 (0.68s)</t>
+          <t>2026-05-25 15:43:44 (0.43s)</t>
         </is>
       </c>
       <c r="N65" s="11" t="n"/>
@@ -15079,7 +15234,7 @@
       </c>
       <c r="M66" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:46:11 (0.51s)</t>
+          <t>2026-05-25 15:43:44 (0.35s)</t>
         </is>
       </c>
       <c r="N66" s="11" t="n"/>
@@ -15139,7 +15294,7 @@
       </c>
       <c r="M67" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:46:12 (1.22s)</t>
+          <t>2026-05-25 15:43:45 (0.53s)</t>
         </is>
       </c>
       <c r="N67" s="11" t="n"/>
@@ -15195,7 +15350,7 @@
       <c r="L68" s="96" t="inlineStr"/>
       <c r="M68" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:46:12 (0.01s)</t>
+          <t>2026-05-25 15:43:45 (0.01s)</t>
         </is>
       </c>
       <c r="N68" s="11" t="n"/>
@@ -15255,7 +15410,7 @@
       </c>
       <c r="M69" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:46:12 (0.00s)</t>
+          <t>2026-05-25 15:43:45 (0.00s)</t>
         </is>
       </c>
       <c r="N69" s="11" t="n"/>
@@ -15315,7 +15470,7 @@
       </c>
       <c r="M70" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:46:12 (0.00s)</t>
+          <t>2026-05-25 15:43:45 (0.00s)</t>
         </is>
       </c>
       <c r="N70" s="11" t="n"/>
@@ -15371,7 +15526,7 @@
       <c r="L71" s="96" t="inlineStr"/>
       <c r="M71" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:46:15 (2.60s)</t>
+          <t>2026-05-25 15:43:47 (2.57s)</t>
         </is>
       </c>
       <c r="N71" s="11" t="n"/>
@@ -15431,7 +15586,7 @@
       </c>
       <c r="M72" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:46:15 (0.00s)</t>
+          <t>2026-05-25 15:43:47 (0.00s)</t>
         </is>
       </c>
       <c r="N72" s="11" t="n"/>
@@ -15491,7 +15646,7 @@
       </c>
       <c r="M73" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:46:18 (3.08s)</t>
+          <t>2026-05-25 15:43:50 (2.61s)</t>
         </is>
       </c>
       <c r="N73" s="11" t="n"/>
@@ -15551,7 +15706,7 @@
       </c>
       <c r="M74" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:46:38 (19.90s)</t>
+          <t>2026-05-25 15:44:10 (19.87s)</t>
         </is>
       </c>
       <c r="N74" s="11" t="n"/>
@@ -15611,7 +15766,7 @@
       </c>
       <c r="M75" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:46:58 (19.91s)</t>
+          <t>2026-05-25 15:44:30 (19.94s)</t>
         </is>
       </c>
       <c r="N75" s="11" t="n"/>
@@ -15671,7 +15826,7 @@
       </c>
       <c r="M76" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:47:15 (16.91s)</t>
+          <t>2026-05-25 15:44:47 (16.99s)</t>
         </is>
       </c>
       <c r="N76" s="11" t="n"/>
@@ -15731,7 +15886,7 @@
       </c>
       <c r="M77" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:47:15 (0.00s)</t>
+          <t>2026-05-25 15:44:47 (0.00s)</t>
         </is>
       </c>
       <c r="N77" s="11" t="n"/>
@@ -15791,7 +15946,7 @@
       </c>
       <c r="M78" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:47:15 (0.00s)</t>
+          <t>2026-05-25 15:44:47 (0.00s)</t>
         </is>
       </c>
       <c r="N78" s="11" t="n"/>
@@ -15857,7 +16012,7 @@
         </is>
       </c>
       <c r="K83" s="75" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="84">
@@ -15875,7 +16030,7 @@
         </is>
       </c>
       <c r="K84" s="75" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -16211,12 +16366,12 @@
       </c>
       <c r="L12" s="101" t="inlineStr">
         <is>
-          <t>HTTP 200 OK | AssertionError: [UI] Folder 'ui_66399160' did not appear in the file manager</t>
+          <t>HTTP 200 OK | AssertionError: [UI] Folder 'ui_c3344610' did not appear in the file manager</t>
         </is>
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:47:48 (21.15s)</t>
+          <t>2026-05-25 15:45:20 (21.30s)</t>
         </is>
       </c>
     </row>
@@ -16275,7 +16430,7 @@
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:47:48 (0.32s)</t>
+          <t>2026-05-25 15:45:21 (0.17s)</t>
         </is>
       </c>
     </row>
@@ -16334,7 +16489,7 @@
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:47:49 (0.67s)</t>
+          <t>2026-05-25 15:45:21 (0.57s)</t>
         </is>
       </c>
     </row>
@@ -16393,7 +16548,7 @@
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:47:50 (0.35s)</t>
+          <t>2026-05-25 15:45:22 (0.21s)</t>
         </is>
       </c>
     </row>
@@ -16452,7 +16607,7 @@
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:47:50 (0.33s)</t>
+          <t>2026-05-25 15:45:22 (0.38s)</t>
         </is>
       </c>
     </row>
@@ -16511,7 +16666,7 @@
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:47:53 (3.04s)</t>
+          <t>2026-05-25 15:45:26 (3.16s)</t>
         </is>
       </c>
     </row>
@@ -16570,7 +16725,7 @@
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:47:54 (0.18s)</t>
+          <t>2026-05-25 15:45:26 (0.23s)</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16784,7 @@
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:47:54 (0.00s)</t>
+          <t>2026-05-25 15:45:26 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -16688,7 +16843,7 @@
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:48:02 (8.33s)</t>
+          <t>2026-05-25 15:45:34 (7.87s)</t>
         </is>
       </c>
     </row>
@@ -16747,7 +16902,7 @@
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:48:02 (0.00s)</t>
+          <t>2026-05-25 15:45:34 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -16806,7 +16961,7 @@
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:48:02 (0.00s)</t>
+          <t>2026-05-25 15:45:34 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -16865,7 +17020,7 @@
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:48:02 (0.00s)</t>
+          <t>2026-05-25 15:45:34 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -16924,7 +17079,7 @@
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:48:02 (0.00s)</t>
+          <t>2026-05-25 15:45:34 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -16983,7 +17138,7 @@
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:48:02 (0.00s)</t>
+          <t>2026-05-25 15:45:34 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17042,7 +17197,7 @@
       </c>
       <c r="M26" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:48:02 (0.00s)</t>
+          <t>2026-05-25 15:45:34 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17101,7 +17256,7 @@
       </c>
       <c r="M27" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:48:02 (0.00s)</t>
+          <t>2026-05-25 15:45:34 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17160,7 +17315,7 @@
       </c>
       <c r="M28" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:48:02 (0.00s)</t>
+          <t>2026-05-25 15:45:34 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17219,7 +17374,7 @@
       </c>
       <c r="M29" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:48:02 (0.00s)</t>
+          <t>2026-05-25 15:45:34 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17278,7 +17433,7 @@
       </c>
       <c r="M30" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:48:02 (0.00s)</t>
+          <t>2026-05-25 15:45:34 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17337,7 +17492,7 @@
       </c>
       <c r="M31" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:48:02 (0.00s)</t>
+          <t>2026-05-25 15:45:34 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17396,7 +17551,7 @@
       </c>
       <c r="M32" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:48:02 (0.00s)</t>
+          <t>2026-05-25 15:45:34 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17455,7 +17610,7 @@
       </c>
       <c r="M33" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:48:02 (0.00s)</t>
+          <t>2026-05-25 15:45:34 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17514,7 +17669,7 @@
       </c>
       <c r="M34" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:48:02 (0.00s)</t>
+          <t>2026-05-25 15:45:34 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -17884,7 +18039,7 @@
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:48:32 (18.49s)</t>
+          <t>2026-05-25 15:46:05 (18.80s)</t>
         </is>
       </c>
     </row>
@@ -17943,7 +18098,7 @@
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:48:38 (5.01s)</t>
+          <t>2026-05-25 15:46:12 (6.28s)</t>
         </is>
       </c>
     </row>
@@ -18002,7 +18157,7 @@
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:49:07 (29.28s)</t>
+          <t>2026-05-25 15:46:45 (32.82s)</t>
         </is>
       </c>
     </row>
@@ -18061,7 +18216,7 @@
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:49:17 (9.65s)</t>
+          <t>2026-05-25 15:46:55 (10.01s)</t>
         </is>
       </c>
     </row>
@@ -18116,7 +18271,7 @@
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:49:26 (9.37s)</t>
+          <t>2026-05-25 15:47:05 (10.05s)</t>
         </is>
       </c>
     </row>
@@ -18175,7 +18330,7 @@
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:50:08 (41.69s)</t>
+          <t>2026-05-25 15:47:16 (11.80s)</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18389,7 @@
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:50:18 (10.13s)</t>
+          <t>2026-05-25 15:47:26 (10.01s)</t>
         </is>
       </c>
     </row>
@@ -18293,7 +18448,7 @@
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:50:30 (12.05s)</t>
+          <t>2026-05-25 15:47:39 (12.85s)</t>
         </is>
       </c>
     </row>
@@ -18352,7 +18507,7 @@
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:50:40 (9.75s)</t>
+          <t>2026-05-25 15:47:49 (9.59s)</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18566,7 @@
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:50:40 (0.18s)</t>
+          <t>2026-05-25 15:47:49 (0.18s)</t>
         </is>
       </c>
     </row>
@@ -18470,7 +18625,7 @@
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-05-21 14:50:40 (0.00s)</t>
+          <t>2026-05-25 15:47:49 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -18828,7 +18983,7 @@
       </c>
       <c r="M12" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:50:57 (1.92s)</t>
+          <t>2026-05-25 15:48:07 (2.15s)</t>
         </is>
       </c>
     </row>
@@ -18886,7 +19041,7 @@
       </c>
       <c r="M13" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:50:59 (1.86s)</t>
+          <t>2026-05-25 15:48:09 (2.02s)</t>
         </is>
       </c>
     </row>
@@ -18944,7 +19099,7 @@
       </c>
       <c r="M14" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:51:01 (1.86s)</t>
+          <t>2026-05-25 15:48:11 (2.03s)</t>
         </is>
       </c>
     </row>
@@ -19002,7 +19157,7 @@
       </c>
       <c r="M15" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:51:03 (1.92s)</t>
+          <t>2026-05-25 15:48:13 (2.04s)</t>
         </is>
       </c>
     </row>
@@ -19060,7 +19215,7 @@
       </c>
       <c r="M16" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:51:07 (3.94s)</t>
+          <t>2026-05-25 15:48:18 (4.07s)</t>
         </is>
       </c>
     </row>
@@ -19118,7 +19273,7 @@
       </c>
       <c r="M17" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:51:10 (3.55s)</t>
+          <t>2026-05-25 15:48:21 (3.62s)</t>
         </is>
       </c>
     </row>
@@ -19176,7 +19331,7 @@
       </c>
       <c r="M18" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:51:15 (4.41s)</t>
+          <t>2026-05-25 15:48:26 (4.94s)</t>
         </is>
       </c>
     </row>
@@ -19234,7 +19389,7 @@
       </c>
       <c r="M19" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:51:17 (1.91s)</t>
+          <t>2026-05-25 15:48:28 (2.11s)</t>
         </is>
       </c>
     </row>
@@ -19292,7 +19447,7 @@
       </c>
       <c r="M20" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:51:21 (4.27s)</t>
+          <t>2026-05-25 15:48:33 (4.44s)</t>
         </is>
       </c>
     </row>
@@ -19346,7 +19501,7 @@
       <c r="L21" s="105" t="inlineStr"/>
       <c r="M21" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:51:34 (12.90s)</t>
+          <t>2026-05-25 15:48:46 (13.01s)</t>
         </is>
       </c>
     </row>
@@ -19400,7 +19555,7 @@
       <c r="L22" s="105" t="inlineStr"/>
       <c r="M22" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:51:47 (12.81s)</t>
+          <t>2026-05-25 15:48:59 (12.90s)</t>
         </is>
       </c>
     </row>
@@ -19453,12 +19608,12 @@
       </c>
       <c r="L23" s="105" t="inlineStr">
         <is>
-          <t>HTTP 200 OK</t>
+          <t>HTTP 0</t>
         </is>
       </c>
       <c r="M23" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:51:51 (3.83s)</t>
+          <t>2026-05-25 15:49:00 (1.47s)</t>
         </is>
       </c>
     </row>
@@ -19516,7 +19671,7 @@
       </c>
       <c r="M24" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:51:55 (4.00s)</t>
+          <t>2026-05-25 15:49:05 (4.01s)</t>
         </is>
       </c>
     </row>
@@ -19574,7 +19729,7 @@
       </c>
       <c r="M25" s="76" t="inlineStr">
         <is>
-          <t>2026-05-21 14:52:02 (7.33s)</t>
+          <t>2026-05-25 15:49:13 (7.63s)</t>
         </is>
       </c>
     </row>

--- a/Data Set/Teamsync_new_testcases.xlsx
+++ b/Data Set/Teamsync_new_testcases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6830" tabRatio="600" firstSheet="6" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6830" tabRatio="600" firstSheet="4" activeTab="9" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,12 +15,13 @@
     <sheet name="Rename" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Move" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Create Shortcut" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TAG-Phase2" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="DBtalk - Phase2" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Tag" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="DBtalk " sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="RBAC" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Share" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Trash" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Version &amp; Compare" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Advance search" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -144,6 +145,43 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF9C5700"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00006100"/>
     </font>
@@ -163,7 +201,7 @@
       <color rgb="009C0006"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="28">
     <fill>
       <patternFill/>
     </fill>
@@ -255,6 +293,38 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6B6B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -398,7 +468,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -647,69 +717,109 @@
     <xf numFmtId="0" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1582,7 +1692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="17.90625" customWidth="1" style="57" min="1" max="1"/>
@@ -1676,6 +1786,7 @@
       <c r="B7" s="49" t="n"/>
     </row>
     <row r="8" ht="29" customHeight="1" s="29"/>
+    <row r="9"/>
     <row r="10" ht="43.5" customHeight="1" s="29">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -1791,6 +1902,21 @@
           <t>201 Created</t>
         </is>
       </c>
+      <c r="K12" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L12" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M12" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:14:20 (2.62s)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="29" customHeight="1" s="29">
       <c r="B13" t="inlineStr">
@@ -1833,6 +1959,17 @@
           <t>201 Created</t>
         </is>
       </c>
+      <c r="K13" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L13" s="134" t="inlineStr"/>
+      <c r="M13" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:14:23 (0.63s)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -1875,6 +2012,21 @@
           <t>200 OK</t>
         </is>
       </c>
+      <c r="K14" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L14" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: [UI] No file in the drive to tag</t>
+        </is>
+      </c>
+      <c r="M14" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:14:29 (2.57s)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="29" customHeight="1" s="29">
       <c r="B15" t="inlineStr">
@@ -1917,6 +2069,21 @@
           <t>200 OK</t>
         </is>
       </c>
+      <c r="K15" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L15" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: [UI] No folder in the drive to tag</t>
+        </is>
+      </c>
+      <c r="M15" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:14:34 (2.57s)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
@@ -1959,6 +2126,21 @@
           <t>200 OK</t>
         </is>
       </c>
+      <c r="K16" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L16" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: [UI] No tagged file in the drive to remove a tag from</t>
+        </is>
+      </c>
+      <c r="M16" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:14:36 (0.02s)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="29" customHeight="1" s="29">
       <c r="B17" t="inlineStr">
@@ -2001,6 +2183,21 @@
           <t>200 OK</t>
         </is>
       </c>
+      <c r="K17" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L17" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: [DATA] No tagged file in the drive to search for</t>
+        </is>
+      </c>
+      <c r="M17" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:14:39 (0.02s)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
@@ -2043,6 +2240,21 @@
           <t>200 OK</t>
         </is>
       </c>
+      <c r="K18" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L18" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: [DATA] No tagged file in the drive to filter by</t>
+        </is>
+      </c>
+      <c r="M18" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:14:42 (0.02s)</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="29" customHeight="1" s="29">
       <c r="B19" t="inlineStr">
@@ -2085,6 +2297,21 @@
           <t>SKIPPED</t>
         </is>
       </c>
+      <c r="K19" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L19" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: TC_Tag_08 | NOT AUTOMATABLE yet — no rename/edit-theme endpoint or UI has been provided. Need the edit-tag flow (PUT/PATCH themes) to implement.</t>
+        </is>
+      </c>
+      <c r="M19" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:14:42 (0.00s)</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="29" customHeight="1" s="29">
       <c r="B20" t="inlineStr">
@@ -2127,6 +2354,17 @@
           <t>200 OK</t>
         </is>
       </c>
+      <c r="K20" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L20" s="134" t="inlineStr"/>
+      <c r="M20" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:14:47 (2.74s)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -2169,6 +2407,21 @@
           <t>409 Conflict</t>
         </is>
       </c>
+      <c r="K21" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L21" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 409 Conflict</t>
+        </is>
+      </c>
+      <c r="M21" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:14:50 (0.19s)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
@@ -2211,6 +2464,17 @@
           <t>400 Bad Request</t>
         </is>
       </c>
+      <c r="K22" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L22" s="134" t="inlineStr"/>
+      <c r="M22" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:14:59 (6.10s)</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="29" customHeight="1" s="29">
       <c r="B23" t="inlineStr">
@@ -2253,6 +2517,17 @@
           <t>400 Bad Request</t>
         </is>
       </c>
+      <c r="K23" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L23" s="134" t="inlineStr"/>
+      <c r="M23" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:15:04 (2.14s)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="29" customHeight="1" s="29">
       <c r="B24" t="inlineStr">
@@ -2295,6 +2570,21 @@
           <t>403 Forbidden</t>
         </is>
       </c>
+      <c r="K24" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L24" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: TC_Tag_13 | NOT TESTABLE — needs a file the logged-in user has no write permission on (a restricted/foreign file fixture), which this single-account env doesn't provide.</t>
+        </is>
+      </c>
+      <c r="M24" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:15:04 (0.00s)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
@@ -2337,6 +2627,21 @@
           <t>404 Not Found</t>
         </is>
       </c>
+      <c r="K25" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L25" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="M25" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:15:07 (0.23s)</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="29" customHeight="1" s="29">
       <c r="B26" t="inlineStr">
@@ -2379,6 +2684,21 @@
           <t>404 Not Found</t>
         </is>
       </c>
+      <c r="K26" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L26" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 500 Internal Server Error</t>
+        </is>
+      </c>
+      <c r="M26" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:15:09 (0.19s)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -2421,6 +2741,21 @@
           <t>200 OK</t>
         </is>
       </c>
+      <c r="K27" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L27" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M27" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:15:20 (7.33s)</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="29" customHeight="1" s="29">
       <c r="B28" t="inlineStr">
@@ -2463,6 +2798,21 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
+      <c r="K28" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L28" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: TC_Tag_17 | NOT TESTABLE on demand — a real 500 from the themes backend cannot be forced from the client without fault injection.</t>
+        </is>
+      </c>
+      <c r="M28" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:15:20 (0.00s)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
@@ -2505,6 +2855,21 @@
           <t>200 OK</t>
         </is>
       </c>
+      <c r="K29" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L29" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: [UI] No file in the drive</t>
+        </is>
+      </c>
+      <c r="M29" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:15:22 (0.02s)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
@@ -2547,6 +2912,17 @@
           <t>200 OK</t>
         </is>
       </c>
+      <c r="K30" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L30" s="134" t="inlineStr"/>
+      <c r="M30" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:15:27 (2.09s)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
@@ -2589,6 +2965,21 @@
           <t>200 OK</t>
         </is>
       </c>
+      <c r="K31" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L31" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: [DATA] No tagged file in the drive to check colour</t>
+        </is>
+      </c>
+      <c r="M31" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:15:29 (0.02s)</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="29" customHeight="1" s="29">
       <c r="B32" t="inlineStr">
@@ -2631,6 +3022,21 @@
           <t>-</t>
         </is>
       </c>
+      <c r="K32" s="137" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="L32" s="138" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK | AssertionError: [UI] No success snackbar after tag creation</t>
+        </is>
+      </c>
+      <c r="M32" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:15:39 (7.40s)</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="29" customHeight="1" s="29">
       <c r="B33" t="inlineStr">
@@ -2673,6 +3079,21 @@
           <t>400 Bad Request</t>
         </is>
       </c>
+      <c r="K33" s="137" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="L33" s="138" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK | AssertionError: [UI] No error feedback on duplicate tag create</t>
+        </is>
+      </c>
+      <c r="M33" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:15:48 (6.43s)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
@@ -2715,6 +3136,21 @@
           <t>200 OK</t>
         </is>
       </c>
+      <c r="K34" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L34" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: TC_Tag_23 | Deferred — depends on the currently-broken assign flow (change-file-themes) to seed a tagged file, plus a rename. Enable once assign works; then: tag a fresh file, rename it, assert the chip persists.</t>
+        </is>
+      </c>
+      <c r="M34" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:15:48 (0.00s)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
@@ -2757,6 +3193,21 @@
           <t>200 OK</t>
         </is>
       </c>
+      <c r="K35" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L35" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: TC_Tag_24 | Deferred — depends on the currently-broken assign flow to seed a tagged file, plus a move. Enable once assign works.</t>
+        </is>
+      </c>
+      <c r="M35" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:15:48 (0.00s)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
@@ -2799,6 +3250,21 @@
           <t>200 OK</t>
         </is>
       </c>
+      <c r="K36" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L36" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: TC_Tag_25 | Deferred — needs a freshly tagged file to delete (depends on the broken assign flow); deleting an existing tagged user file is destructive.</t>
+        </is>
+      </c>
+      <c r="M36" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:15:48 (0.00s)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
@@ -2841,7 +3307,24 @@
           <t>200 OK</t>
         </is>
       </c>
-    </row>
+      <c r="K37" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L37" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: TC_Tag_26 | Deferred — meaningful concurrent tagging needs the assign flow (change-file-themes) to actually work; it currently 500s. Enable once assign is fixed, then assign two tags to one real file in parallel and assert both land with no conflict.</t>
+        </is>
+      </c>
+      <c r="M37" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:15:48 (0.00s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40" ht="31" customHeight="1" s="29">
       <c r="A40" s="51" t="inlineStr">
         <is>
@@ -2863,6 +3346,9 @@
           <t>Total Test Cases</t>
         </is>
       </c>
+      <c r="J40" s="76" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="41" ht="31" customHeight="1" s="29">
       <c r="B41" s="58" t="inlineStr">
@@ -2876,7 +3362,9 @@
           <t>Executed Test Cases</t>
         </is>
       </c>
-      <c r="J41" s="53" t="n"/>
+      <c r="J41" s="77" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="42" ht="31" customHeight="1" s="29">
       <c r="B42" s="58" t="inlineStr">
@@ -2890,7 +3378,9 @@
           <t>Passed Test Cases</t>
         </is>
       </c>
-      <c r="J42" s="53" t="n"/>
+      <c r="J42" s="77" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="43" ht="31" customHeight="1" s="29">
       <c r="B43" s="58" t="inlineStr">
@@ -2904,7 +3394,9 @@
           <t>Failed Test Cases</t>
         </is>
       </c>
-      <c r="J43" s="53" t="n"/>
+      <c r="J43" s="77" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="44" ht="31" customHeight="1" s="29">
       <c r="B44" s="58" t="inlineStr">
@@ -2918,7 +3410,9 @@
           <t>Blocked Test Cases</t>
         </is>
       </c>
-      <c r="J44" s="53" t="n"/>
+      <c r="J44" s="77" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="45" ht="31" customHeight="1" s="29">
       <c r="B45" s="58" t="inlineStr">
@@ -2932,8 +3426,14 @@
           <t>Not Executed Test Cases</t>
         </is>
       </c>
-      <c r="J45" s="53" t="n"/>
-    </row>
+      <c r="J45" s="77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7774,15 +8274,15 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K12" s="104" t="inlineStr">
+      <c r="K12" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="105" t="inlineStr"/>
+      <c r="L12" s="130" t="inlineStr"/>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:01 (4.66s)</t>
+          <t>2026-06-18 15:02:35 (4.10s)</t>
         </is>
       </c>
     </row>
@@ -7829,19 +8329,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="105" t="inlineStr">
+      <c r="L13" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:02 (1.01s)</t>
+          <t>2026-06-18 15:02:36 (0.90s)</t>
         </is>
       </c>
     </row>
@@ -7888,19 +8388,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="105" t="inlineStr">
+      <c r="L14" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:05 (2.80s)</t>
+          <t>2026-06-18 15:02:39 (2.67s)</t>
         </is>
       </c>
     </row>
@@ -7947,19 +8447,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="105" t="inlineStr">
+      <c r="L15" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:06 (0.87s)</t>
+          <t>2026-06-18 15:02:39 (0.85s)</t>
         </is>
       </c>
     </row>
@@ -8006,19 +8506,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="105" t="inlineStr">
+      <c r="L16" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:07 (1.21s)</t>
+          <t>2026-06-18 15:02:41 (1.16s)</t>
         </is>
       </c>
     </row>
@@ -8065,19 +8565,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K17" s="104" t="inlineStr">
+      <c r="K17" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L17" s="105" t="inlineStr">
+      <c r="L17" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:08 (1.02s)</t>
+          <t>2026-06-18 15:02:41 (0.93s)</t>
         </is>
       </c>
     </row>
@@ -8124,19 +8624,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K18" s="104" t="inlineStr">
+      <c r="K18" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L18" s="105" t="inlineStr">
+      <c r="L18" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:09 (1.05s)</t>
+          <t>2026-06-18 15:02:42 (0.97s)</t>
         </is>
       </c>
     </row>
@@ -8183,19 +8683,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K19" s="104" t="inlineStr">
+      <c r="K19" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L19" s="105" t="inlineStr">
+      <c r="L19" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:10 (0.97s)</t>
+          <t>2026-06-18 15:02:43 (0.88s)</t>
         </is>
       </c>
     </row>
@@ -8242,19 +8742,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K20" s="104" t="inlineStr">
+      <c r="K20" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L20" s="105" t="inlineStr">
+      <c r="L20" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:11 (1.04s)</t>
+          <t>2026-06-18 15:02:44 (1.00s)</t>
         </is>
       </c>
     </row>
@@ -8301,19 +8801,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K21" s="104" t="inlineStr">
+      <c r="K21" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L21" s="105" t="inlineStr">
+      <c r="L21" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:12 (1.17s)</t>
+          <t>2026-06-18 15:02:45 (1.11s)</t>
         </is>
       </c>
     </row>
@@ -8360,19 +8860,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K22" s="104" t="inlineStr">
+      <c r="K22" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L22" s="105" t="inlineStr">
+      <c r="L22" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:13 (1.17s)</t>
+          <t>2026-06-18 15:02:47 (1.14s)</t>
         </is>
       </c>
     </row>
@@ -8419,19 +8919,19 @@
           <t>409 Conflict – Duplicate resource</t>
         </is>
       </c>
-      <c r="K23" s="104" t="inlineStr">
+      <c r="K23" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L23" s="105" t="inlineStr">
+      <c r="L23" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:15 (1.25s)</t>
+          <t>2026-06-18 15:02:48 (1.15s)</t>
         </is>
       </c>
     </row>
@@ -8478,19 +8978,19 @@
           <t>400 Bad Request – Missing required input</t>
         </is>
       </c>
-      <c r="K24" s="108" t="inlineStr">
+      <c r="K24" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L24" s="109" t="inlineStr">
+      <c r="L24" s="132" t="inlineStr">
         <is>
           <t>HTTP 200 OK | AssertionError: [API] Expected 400/422 for empty usernames, got 200</t>
         </is>
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:16 (0.98s)</t>
+          <t>2026-06-18 15:02:49 (0.88s)</t>
         </is>
       </c>
     </row>
@@ -8537,19 +9037,19 @@
           <t>400 Bad Request – Invalid input format</t>
         </is>
       </c>
-      <c r="K25" s="108" t="inlineStr">
+      <c r="K25" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L25" s="109" t="inlineStr">
+      <c r="L25" s="132" t="inlineStr">
         <is>
           <t>HTTP 200 OK | AssertionError: [API] Expected 400/422 for invalid email, got 200</t>
         </is>
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:17 (0.99s)</t>
+          <t>2026-06-18 15:02:50 (0.89s)</t>
         </is>
       </c>
     </row>
@@ -8596,19 +9096,19 @@
           <t>403 Forbidden – Action not allowed</t>
         </is>
       </c>
-      <c r="K26" s="104" t="inlineStr">
+      <c r="K26" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L26" s="105" t="inlineStr">
+      <c r="L26" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M26" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:18 (1.00s)</t>
+          <t>2026-06-18 15:02:50 (0.88s)</t>
         </is>
       </c>
     </row>
@@ -8655,19 +9155,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K27" s="106" t="inlineStr">
+      <c r="K27" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L27" s="107" t="inlineStr">
+      <c r="L27" s="131" t="inlineStr">
         <is>
           <t>Skipped: Skipped per project decision — server JVM heap is limited; large-file scenarios are tested by Upload module</t>
         </is>
       </c>
       <c r="M27" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:18 (0.00s)</t>
+          <t>2026-06-18 15:02:50 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -8714,19 +9214,19 @@
           <t>400 Bad Request – Invalid filename</t>
         </is>
       </c>
-      <c r="K28" s="104" t="inlineStr">
+      <c r="K28" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L28" s="105" t="inlineStr">
+      <c r="L28" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M28" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:20 (2.40s)</t>
+          <t>2026-06-18 15:02:53 (2.40s)</t>
         </is>
       </c>
     </row>
@@ -8773,19 +9273,19 @@
           <t>503 Service Unavailable – Network/server issue</t>
         </is>
       </c>
-      <c r="K29" s="106" t="inlineStr">
+      <c r="K29" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L29" s="107" t="inlineStr">
+      <c r="L29" s="131" t="inlineStr">
         <is>
           <t>Skipped: Hard to simulate true network failure deterministically — would need a proxy/middleware that drops connections</t>
         </is>
       </c>
       <c r="M29" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:20 (0.00s)</t>
+          <t>2026-06-18 15:02:53 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -8832,19 +9332,19 @@
           <t>401 Unauthorized – Authentication required</t>
         </is>
       </c>
-      <c r="K30" s="104" t="inlineStr">
+      <c r="K30" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L30" s="105" t="inlineStr">
+      <c r="L30" s="130" t="inlineStr">
         <is>
           <t>HTTP 401 Unauthorized</t>
         </is>
       </c>
       <c r="M30" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:21 (0.80s)</t>
+          <t>2026-06-18 15:02:54 (0.74s)</t>
         </is>
       </c>
     </row>
@@ -8891,19 +9391,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K31" s="104" t="inlineStr">
+      <c r="K31" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L31" s="105" t="inlineStr">
+      <c r="L31" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M31" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:22 (1.25s)</t>
+          <t>2026-06-18 15:02:55 (1.28s)</t>
         </is>
       </c>
     </row>
@@ -8950,19 +9450,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K32" s="104" t="inlineStr">
+      <c r="K32" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L32" s="105" t="inlineStr">
+      <c r="L32" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M32" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:25 (2.68s)</t>
+          <t>2026-06-18 15:02:58 (2.61s)</t>
         </is>
       </c>
     </row>
@@ -9009,19 +9509,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K33" s="106" t="inlineStr">
+      <c r="K33" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L33" s="107" t="inlineStr">
+      <c r="L33" s="131" t="inlineStr">
         <is>
           <t>Skipped: [UI] Search/find didn't surface the freshly created file</t>
         </is>
       </c>
       <c r="M33" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:29 (3.70s)</t>
+          <t>2026-06-18 15:03:01 (3.27s)</t>
         </is>
       </c>
     </row>
@@ -9072,19 +9572,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K34" s="104" t="inlineStr">
+      <c r="K34" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L34" s="105" t="inlineStr">
+      <c r="L34" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M34" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:30 (1.29s)</t>
+          <t>2026-06-18 15:03:02 (1.01s)</t>
         </is>
       </c>
     </row>
@@ -9131,19 +9631,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K35" s="104" t="inlineStr">
+      <c r="K35" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L35" s="105" t="inlineStr">
+      <c r="L35" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M35" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:11 (1.03s)</t>
+          <t>2026-06-18 15:23:32 (0.96s)</t>
         </is>
       </c>
     </row>
@@ -9190,19 +9690,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K36" s="104" t="inlineStr">
+      <c r="K36" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L36" s="105" t="inlineStr">
+      <c r="L36" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M36" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:12 (1.06s)</t>
+          <t>2026-06-18 15:23:33 (0.94s)</t>
         </is>
       </c>
     </row>
@@ -9249,19 +9749,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K37" s="104" t="inlineStr">
+      <c r="K37" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L37" s="105" t="inlineStr">
+      <c r="L37" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M37" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:13 (0.99s)</t>
+          <t>2026-06-18 15:23:34 (1.05s)</t>
         </is>
       </c>
     </row>
@@ -9308,19 +9808,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K38" s="104" t="inlineStr">
+      <c r="K38" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L38" s="105" t="inlineStr">
+      <c r="L38" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M38" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:14 (0.98s)</t>
+          <t>2026-06-18 15:23:35 (1.00s)</t>
         </is>
       </c>
     </row>
@@ -9367,19 +9867,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K39" s="106" t="inlineStr">
+      <c r="K39" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L39" s="107" t="inlineStr">
+      <c r="L39" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'csv' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M39" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:14 (0.00s)</t>
+          <t>2026-06-18 15:23:35 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -9426,19 +9926,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K40" s="104" t="inlineStr">
+      <c r="K40" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L40" s="105" t="inlineStr">
+      <c r="L40" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M40" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:15 (0.95s)</t>
+          <t>2026-06-18 15:23:36 (0.92s)</t>
         </is>
       </c>
     </row>
@@ -9485,19 +9985,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K41" s="104" t="inlineStr">
+      <c r="K41" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L41" s="105" t="inlineStr">
+      <c r="L41" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M41" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:16 (0.99s)</t>
+          <t>2026-06-18 15:23:37 (0.96s)</t>
         </is>
       </c>
     </row>
@@ -9544,19 +10044,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K42" s="104" t="inlineStr">
+      <c r="K42" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L42" s="105" t="inlineStr">
+      <c r="L42" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M42" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:17 (1.05s)</t>
+          <t>2026-06-18 15:23:38 (1.01s)</t>
         </is>
       </c>
     </row>
@@ -9603,19 +10103,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K43" s="104" t="inlineStr">
+      <c r="K43" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L43" s="105" t="inlineStr">
+      <c r="L43" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M43" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:18 (0.97s)</t>
+          <t>2026-06-18 15:23:39 (0.97s)</t>
         </is>
       </c>
     </row>
@@ -9662,19 +10162,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K44" s="106" t="inlineStr">
+      <c r="K44" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L44" s="107" t="inlineStr">
+      <c r="L44" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'xml' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M44" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:18 (0.23s)</t>
+          <t>2026-06-18 15:23:40 (0.23s)</t>
         </is>
       </c>
     </row>
@@ -9721,19 +10221,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K45" s="104" t="inlineStr">
+      <c r="K45" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L45" s="105" t="inlineStr">
+      <c r="L45" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M45" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:19 (0.94s)</t>
+          <t>2026-06-18 15:23:41 (1.01s)</t>
         </is>
       </c>
     </row>
@@ -9780,19 +10280,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K46" s="104" t="inlineStr">
+      <c r="K46" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L46" s="105" t="inlineStr">
+      <c r="L46" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M46" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:20 (0.93s)</t>
+          <t>2026-06-18 15:23:41 (0.93s)</t>
         </is>
       </c>
     </row>
@@ -9839,19 +10339,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K47" s="106" t="inlineStr">
+      <c r="K47" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L47" s="107" t="inlineStr">
+      <c r="L47" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'rar' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M47" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:20 (0.00s)</t>
+          <t>2026-06-18 15:23:41 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -9898,19 +10398,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K48" s="104" t="inlineStr">
+      <c r="K48" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L48" s="105" t="inlineStr">
+      <c r="L48" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M48" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:21 (1.04s)</t>
+          <t>2026-06-18 15:23:43 (1.06s)</t>
         </is>
       </c>
     </row>
@@ -9957,19 +10457,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K49" s="106" t="inlineStr">
+      <c r="K49" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L49" s="107" t="inlineStr">
+      <c r="L49" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'tar' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M49" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:22 (1.33s)</t>
+          <t>2026-06-18 15:23:44 (1.42s)</t>
         </is>
       </c>
     </row>
@@ -10016,19 +10516,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K50" s="104" t="inlineStr">
+      <c r="K50" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L50" s="105" t="inlineStr">
+      <c r="L50" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M50" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:23 (1.05s)</t>
+          <t>2026-06-18 15:23:45 (0.99s)</t>
         </is>
       </c>
     </row>
@@ -10075,19 +10575,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K51" s="104" t="inlineStr">
+      <c r="K51" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L51" s="105" t="inlineStr">
+      <c r="L51" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M51" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:25 (1.14s)</t>
+          <t>2026-06-18 15:23:46 (1.03s)</t>
         </is>
       </c>
     </row>
@@ -10134,19 +10634,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K52" s="104" t="inlineStr">
+      <c r="K52" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L52" s="105" t="inlineStr">
+      <c r="L52" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M52" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:26 (0.93s)</t>
+          <t>2026-06-18 15:23:47 (0.98s)</t>
         </is>
       </c>
     </row>
@@ -10193,19 +10693,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K53" s="104" t="inlineStr">
+      <c r="K53" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L53" s="105" t="inlineStr">
+      <c r="L53" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M53" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:27 (0.99s)</t>
+          <t>2026-06-18 15:23:48 (0.96s)</t>
         </is>
       </c>
     </row>
@@ -10252,19 +10752,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K54" s="104" t="inlineStr">
+      <c r="K54" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L54" s="105" t="inlineStr">
+      <c r="L54" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M54" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:28 (0.98s)</t>
+          <t>2026-06-18 15:23:49 (0.99s)</t>
         </is>
       </c>
     </row>
@@ -10311,19 +10811,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K55" s="106" t="inlineStr">
+      <c r="K55" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L55" s="107" t="inlineStr">
+      <c r="L55" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'tif' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M55" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:28 (0.23s)</t>
+          <t>2026-06-18 15:23:49 (0.25s)</t>
         </is>
       </c>
     </row>
@@ -10370,19 +10870,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K56" s="104" t="inlineStr">
+      <c r="K56" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L56" s="105" t="inlineStr">
+      <c r="L56" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M56" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:29 (1.00s)</t>
+          <t>2026-06-18 15:23:50 (1.00s)</t>
         </is>
       </c>
     </row>
@@ -10429,19 +10929,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K57" s="104" t="inlineStr">
+      <c r="K57" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L57" s="105" t="inlineStr">
+      <c r="L57" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M57" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:30 (0.97s)</t>
+          <t>2026-06-18 15:23:51 (0.97s)</t>
         </is>
       </c>
     </row>
@@ -10488,19 +10988,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K58" s="104" t="inlineStr">
+      <c r="K58" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L58" s="105" t="inlineStr">
+      <c r="L58" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M58" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:31 (0.96s)</t>
+          <t>2026-06-18 15:23:52 (1.06s)</t>
         </is>
       </c>
     </row>
@@ -10547,19 +11047,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K59" s="106" t="inlineStr">
+      <c r="K59" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L59" s="107" t="inlineStr">
+      <c r="L59" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'wav' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M59" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:31 (0.00s)</t>
+          <t>2026-06-18 15:23:52 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -10606,19 +11106,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K60" s="104" t="inlineStr">
+      <c r="K60" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L60" s="105" t="inlineStr">
+      <c r="L60" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M60" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:32 (0.83s)</t>
+          <t>2026-06-18 15:23:53 (1.08s)</t>
         </is>
       </c>
     </row>
@@ -10665,19 +11165,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K61" s="106" t="inlineStr">
+      <c r="K61" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L61" s="107" t="inlineStr">
+      <c r="L61" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'flac' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M61" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:32 (0.00s)</t>
+          <t>2026-06-18 15:23:53 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -10724,19 +11224,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K62" s="104" t="inlineStr">
+      <c r="K62" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L62" s="105" t="inlineStr">
+      <c r="L62" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M62" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:33 (1.26s)</t>
+          <t>2026-06-18 15:23:55 (1.27s)</t>
         </is>
       </c>
     </row>
@@ -10783,19 +11283,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K63" s="104" t="inlineStr">
+      <c r="K63" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L63" s="105" t="inlineStr">
+      <c r="L63" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M63" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:34 (0.99s)</t>
+          <t>2026-06-18 15:23:56 (1.04s)</t>
         </is>
       </c>
     </row>
@@ -10842,19 +11342,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K64" s="104" t="inlineStr">
+      <c r="K64" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L64" s="105" t="inlineStr">
+      <c r="L64" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M64" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:36 (2.04s)</t>
+          <t>2026-06-18 15:23:58 (1.79s)</t>
         </is>
       </c>
     </row>
@@ -10901,19 +11401,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K65" s="104" t="inlineStr">
+      <c r="K65" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L65" s="105" t="inlineStr">
+      <c r="L65" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M65" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:41 (4.67s)</t>
+          <t>2026-06-18 15:24:02 (4.85s)</t>
         </is>
       </c>
     </row>
@@ -10960,19 +11460,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K66" s="104" t="inlineStr">
+      <c r="K66" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L66" s="105" t="inlineStr">
+      <c r="L66" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M66" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:42 (1.17s)</t>
+          <t>2026-06-18 15:24:04 (1.25s)</t>
         </is>
       </c>
     </row>
@@ -11019,19 +11519,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K67" s="106" t="inlineStr">
+      <c r="K67" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L67" s="107" t="inlineStr">
+      <c r="L67" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'wmv' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M67" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:42 (0.27s)</t>
+          <t>2026-06-18 15:24:04 (0.28s)</t>
         </is>
       </c>
     </row>
@@ -11078,19 +11578,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K68" s="106" t="inlineStr">
+      <c r="K68" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L68" s="107" t="inlineStr">
+      <c r="L68" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key '3gpp' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M68" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:43 (0.89s)</t>
+          <t>2026-06-18 15:24:05 (0.72s)</t>
         </is>
       </c>
     </row>
@@ -11137,19 +11637,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K69" s="106" t="inlineStr">
+      <c r="K69" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L69" s="107" t="inlineStr">
+      <c r="L69" s="131" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Fixture key 'flv' not in UPLOAD_FILES or upload failed</t>
         </is>
       </c>
       <c r="M69" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:06:43 (0.29s)</t>
+          <t>2026-06-18 15:24:05 (0.24s)</t>
         </is>
       </c>
     </row>
@@ -11200,19 +11700,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K70" s="106" t="inlineStr">
+      <c r="K70" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L70" s="107" t="inlineStr">
+      <c r="L70" s="131" t="inlineStr">
         <is>
           <t>Skipped: Notification verification requires recipient session — out of scope for owner-only test framework</t>
         </is>
       </c>
       <c r="M70" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:30 (0.00s)</t>
+          <t>2026-06-18 15:03:02 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -11259,19 +11759,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K71" s="104" t="inlineStr">
+      <c r="K71" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L71" s="105" t="inlineStr">
+      <c r="L71" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M71" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:32 (1.49s)</t>
+          <t>2026-06-18 15:03:03 (1.19s)</t>
         </is>
       </c>
     </row>
@@ -11318,19 +11818,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K72" s="104" t="inlineStr">
+      <c r="K72" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L72" s="105" t="inlineStr">
+      <c r="L72" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M72" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:33 (1.21s)</t>
+          <t>2026-06-18 15:03:04 (1.08s)</t>
         </is>
       </c>
     </row>
@@ -11377,19 +11877,19 @@
           <t>403 Forbidden – Access denied</t>
         </is>
       </c>
-      <c r="K73" s="106" t="inlineStr">
+      <c r="K73" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L73" s="107" t="inlineStr">
+      <c r="L73" s="131" t="inlineStr">
         <is>
           <t>Skipped: Requires a second browser session as recipient</t>
         </is>
       </c>
       <c r="M73" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:33 (0.00s)</t>
+          <t>2026-06-18 15:03:04 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -11436,19 +11936,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K74" s="106" t="inlineStr">
+      <c r="K74" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L74" s="107" t="inlineStr">
+      <c r="L74" s="131" t="inlineStr">
         <is>
           <t>Skipped: Requires a second browser session as recipient</t>
         </is>
       </c>
       <c r="M74" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:33 (0.00s)</t>
+          <t>2026-06-18 15:03:04 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -11495,19 +11995,19 @@
           <t>403 Forbidden – Access revoked</t>
         </is>
       </c>
-      <c r="K75" s="106" t="inlineStr">
+      <c r="K75" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L75" s="107" t="inlineStr">
+      <c r="L75" s="131" t="inlineStr">
         <is>
           <t>Skipped: Requires a second browser session as recipient</t>
         </is>
       </c>
       <c r="M75" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:33 (0.00s)</t>
+          <t>2026-06-18 15:03:04 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -11554,19 +12054,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K76" s="106" t="inlineStr">
+      <c r="K76" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L76" s="107" t="inlineStr">
+      <c r="L76" s="131" t="inlineStr">
         <is>
           <t>Skipped: Requires a second browser session as recipient</t>
         </is>
       </c>
       <c r="M76" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:33 (0.00s)</t>
+          <t>2026-06-18 15:03:04 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -11613,19 +12113,19 @@
           <t>404 Not Found – Resource missing</t>
         </is>
       </c>
-      <c r="K77" s="104" t="inlineStr">
+      <c r="K77" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L77" s="105" t="inlineStr">
+      <c r="L77" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M77" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:34 (1.19s)</t>
+          <t>2026-06-18 15:03:05 (1.19s)</t>
         </is>
       </c>
     </row>
@@ -11672,19 +12172,19 @@
           <t>403 Forbidden – User inactive</t>
         </is>
       </c>
-      <c r="K78" s="106" t="inlineStr">
+      <c r="K78" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L78" s="107" t="inlineStr">
+      <c r="L78" s="131" t="inlineStr">
         <is>
           <t>Skipped: Requires a second browser session as recipient</t>
         </is>
       </c>
       <c r="M78" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:34 (0.00s)</t>
+          <t>2026-06-18 15:03:05 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -11731,19 +12231,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K79" s="104" t="inlineStr">
+      <c r="K79" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L79" s="105" t="inlineStr">
+      <c r="L79" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M79" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:35 (1.09s)</t>
+          <t>2026-06-18 15:03:06 (0.97s)</t>
         </is>
       </c>
     </row>
@@ -11790,19 +12290,19 @@
           <t>200 OK – Request successful</t>
         </is>
       </c>
-      <c r="K80" s="106" t="inlineStr">
+      <c r="K80" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L80" s="107" t="inlineStr">
+      <c r="L80" s="131" t="inlineStr">
         <is>
           <t>Skipped: Notification API/UI verification not implemented yet</t>
         </is>
       </c>
       <c r="M80" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:35 (0.00s)</t>
+          <t>2026-06-18 15:03:06 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -11849,19 +12349,19 @@
           <t xml:space="preserve"> - </t>
         </is>
       </c>
-      <c r="K81" s="104" t="inlineStr">
+      <c r="K81" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L81" s="105" t="inlineStr">
+      <c r="L81" s="130" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request</t>
         </is>
       </c>
       <c r="M81" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:49:35 (0.18s)</t>
+          <t>2026-06-18 15:03:07 (0.20s)</t>
         </is>
       </c>
     </row>
@@ -12224,19 +12724,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K12" s="104" t="inlineStr">
+      <c r="K12" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="105" t="inlineStr">
+      <c r="L12" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:01:48 (14.85s)</t>
+          <t>2026-06-18 15:16:16 (14.91s)</t>
         </is>
       </c>
     </row>
@@ -12283,19 +12783,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="105" t="inlineStr">
+      <c r="L13" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:01:53 (4.68s)</t>
+          <t>2026-06-18 15:16:21 (4.66s)</t>
         </is>
       </c>
     </row>
@@ -12342,19 +12842,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="105" t="inlineStr">
+      <c r="L14" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:01:57 (4.14s)</t>
+          <t>2026-06-18 15:16:25 (4.13s)</t>
         </is>
       </c>
     </row>
@@ -12401,19 +12901,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="105" t="inlineStr">
+      <c r="L15" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:02:16 (18.84s)</t>
+          <t>2026-06-18 15:16:39 (13.92s)</t>
         </is>
       </c>
     </row>
@@ -12460,19 +12960,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="105" t="inlineStr">
+      <c r="L16" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:02:21 (4.96s)</t>
+          <t>2026-06-18 15:16:43 (4.74s)</t>
         </is>
       </c>
     </row>
@@ -12519,23 +13019,23 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K17" s="104" t="inlineStr">
+      <c r="K17" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L17" s="105" t="inlineStr">
+      <c r="L17" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:03:39 (78.01s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+          <t>2026-06-18 15:17:27 (43.74s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="72.5" customHeight="1" s="29">
       <c r="A18" s="11" t="n"/>
       <c r="B18" s="11" t="inlineStr">
         <is>
@@ -12578,19 +13078,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K18" s="108" t="inlineStr">
+      <c r="K18" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L18" s="109" t="inlineStr">
+      <c r="L18" s="125" t="inlineStr">
         <is>
           <t>HTTP 200 OK | playwright._impl._errors.TimeoutError: Timeout 20000ms exceeded while waiting for event "response"</t>
         </is>
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:04:08 (29.75s)</t>
+          <t>2026-06-18 15:17:57 (29.54s)</t>
         </is>
       </c>
     </row>
@@ -12637,19 +13137,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K19" s="104" t="inlineStr">
+      <c r="K19" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L19" s="105" t="inlineStr">
+      <c r="L19" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:04:18 (9.06s)</t>
+          <t>2026-06-18 15:18:06 (9.18s)</t>
         </is>
       </c>
     </row>
@@ -12696,19 +13196,19 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K20" s="104" t="inlineStr">
+      <c r="K20" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L20" s="105" t="inlineStr">
+      <c r="L20" s="130" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:04:18 (0.32s)</t>
+          <t>2026-06-18 15:18:06 (0.30s)</t>
         </is>
       </c>
     </row>
@@ -12755,19 +13255,19 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K21" s="106" t="inlineStr">
+      <c r="K21" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L21" s="107" t="inlineStr">
+      <c r="L21" s="131" t="inlineStr">
         <is>
           <t>Skipped: TC_trash_10 | NOT TESTABLE on demand. A real 500 from the empty-trash backend cannot be forced from the test client without server fault injection. Covered indirectly by TC_09's invalid-id rejection.</t>
         </is>
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:04:18 (0.00s)</t>
+          <t>2026-06-18 15:18:06 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -12814,19 +13314,19 @@
           <t>408 Request Timeout</t>
         </is>
       </c>
-      <c r="K22" s="106" t="inlineStr">
+      <c r="K22" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L22" s="107" t="inlineStr">
+      <c r="L22" s="131" t="inlineStr">
         <is>
           <t>Skipped: TC_trash_11 | NOT TESTABLE reliably. Simulating a mid-request network disconnect / 408 from the client is non-deterministic in this harness.</t>
         </is>
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:04:18 (0.00s)</t>
+          <t>2026-06-18 15:18:06 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -12873,19 +13373,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K23" s="106" t="inlineStr">
+      <c r="K23" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L23" s="107" t="inlineStr">
+      <c r="L23" s="131" t="inlineStr">
         <is>
           <t>Skipped: TC_trash_12 | NOT TESTABLE as a failure. The restoreFiles endpoint is lenient — it returns 200 even for a non-existent file id (verified on the live build), so a restore-to-missing-location failure cannot be forced from the client. The happy-path restore is covered by TC_03/TC_04.</t>
         </is>
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:04:18 (0.00s)</t>
+          <t>2026-06-18 15:18:06 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -12932,15 +13432,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K24" s="104" t="inlineStr">
+      <c r="K24" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L24" s="105" t="inlineStr"/>
+      <c r="L24" s="130" t="inlineStr"/>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:04:20 (1.52s)</t>
+          <t>2026-06-18 15:18:08 (1.55s)</t>
         </is>
       </c>
     </row>
@@ -12987,19 +13487,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K25" s="104" t="inlineStr">
+      <c r="K25" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L25" s="105" t="inlineStr">
+      <c r="L25" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:04:30 (10.00s)</t>
+          <t>2026-06-18 15:18:18 (9.99s)</t>
         </is>
       </c>
     </row>
@@ -13046,15 +13546,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K26" s="104" t="inlineStr">
+      <c r="K26" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L26" s="105" t="inlineStr"/>
+      <c r="L26" s="130" t="inlineStr"/>
       <c r="M26" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:04:33 (3.52s)</t>
+          <t>2026-06-18 15:18:21 (3.41s)</t>
         </is>
       </c>
     </row>
@@ -13101,19 +13601,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K27" s="104" t="inlineStr">
+      <c r="K27" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L27" s="105" t="inlineStr">
+      <c r="L27" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M27" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:04:38 (4.47s)</t>
+          <t>2026-06-18 15:18:26 (4.44s)</t>
         </is>
       </c>
     </row>
@@ -13160,19 +13660,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K28" s="104" t="inlineStr">
+      <c r="K28" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L28" s="105" t="inlineStr">
+      <c r="L28" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M28" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:04:59 (21.40s)</t>
+          <t>2026-06-18 15:18:48 (21.94s)</t>
         </is>
       </c>
     </row>
@@ -13219,19 +13719,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K29" s="104" t="inlineStr">
+      <c r="K29" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L29" s="105" t="inlineStr">
+      <c r="L29" s="130" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request</t>
         </is>
       </c>
       <c r="M29" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:04:59 (0.30s)</t>
+          <t>2026-06-18 15:18:48 (0.28s)</t>
         </is>
       </c>
     </row>
@@ -13278,19 +13778,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K30" s="104" t="inlineStr">
+      <c r="K30" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L30" s="105" t="inlineStr">
+      <c r="L30" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M30" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:05:10 (10.98s)</t>
+          <t>2026-06-18 15:18:59 (10.95s)</t>
         </is>
       </c>
     </row>
@@ -13337,19 +13837,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K31" s="104" t="inlineStr">
+      <c r="K31" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L31" s="105" t="inlineStr">
+      <c r="L31" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M31" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:05:22 (11.41s)</t>
+          <t>2026-06-18 15:19:11 (11.46s)</t>
         </is>
       </c>
     </row>
@@ -13396,19 +13896,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K32" s="104" t="inlineStr">
+      <c r="K32" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L32" s="105" t="inlineStr">
+      <c r="L32" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M32" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:05:43 (21.51s)</t>
+          <t>2026-06-18 15:19:32 (21.39s)</t>
         </is>
       </c>
     </row>
@@ -13455,19 +13955,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K33" s="104" t="inlineStr">
+      <c r="K33" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L33" s="105" t="inlineStr">
+      <c r="L33" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M33" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:05:57 (13.45s)</t>
+          <t>2026-06-18 15:19:45 (13.54s)</t>
         </is>
       </c>
     </row>
@@ -15077,6 +15577,1875 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="16.08984375" customWidth="1" style="29" min="1" max="1"/>
+    <col width="18.453125" customWidth="1" style="29" min="2" max="2"/>
+    <col width="45.81640625" customWidth="1" style="29" min="3" max="3"/>
+    <col width="31.26953125" customWidth="1" style="29" min="4" max="4"/>
+    <col width="18.54296875" customWidth="1" style="29" min="5" max="5"/>
+    <col width="17.08984375" customWidth="1" style="29" min="6" max="6"/>
+    <col width="20" customWidth="1" style="29" min="7" max="7"/>
+    <col width="32.36328125" customWidth="1" style="29" min="8" max="8"/>
+    <col width="24.26953125" customWidth="1" style="29" min="9" max="9"/>
+    <col width="19.81640625" customWidth="1" style="29" min="10" max="10"/>
+    <col width="16.453125" customWidth="1" style="29" min="11" max="11"/>
+    <col width="20.08984375" customWidth="1" style="29" min="12" max="12"/>
+    <col width="6.54296875" customWidth="1" style="29" min="13" max="13"/>
+    <col width="8.7265625" customWidth="1" style="29" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="98" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B1" s="97" t="inlineStr">
+        <is>
+          <t>TeamSync v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="98" t="inlineStr">
+        <is>
+          <t>Module Name</t>
+        </is>
+      </c>
+      <c r="B2" s="97" t="inlineStr">
+        <is>
+          <t>Advance Search</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="98" t="inlineStr">
+        <is>
+          <t>Build Version</t>
+        </is>
+      </c>
+      <c r="B3" s="97" t="inlineStr">
+        <is>
+          <t>v1.0.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="98" t="inlineStr">
+        <is>
+          <t>Test Environment</t>
+        </is>
+      </c>
+      <c r="B4" s="97" t="inlineStr">
+        <is>
+          <t>http://frontdms-teamsync.apps.lab.ocp.lan/teamsync/home</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="98" t="inlineStr">
+        <is>
+          <t>Executed By</t>
+        </is>
+      </c>
+      <c r="B5" s="97" t="inlineStr">
+        <is>
+          <t>Ankit tiwari</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="98" t="inlineStr">
+        <is>
+          <t>Execution Date</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="98" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n"/>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="99" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="B10" s="99" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="C10" s="99" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D10" s="99" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E10" s="99" t="inlineStr">
+        <is>
+          <t>Pre-condition</t>
+        </is>
+      </c>
+      <c r="F10" s="99" t="inlineStr">
+        <is>
+          <t>Post-condition</t>
+        </is>
+      </c>
+      <c r="G10" s="99" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="H10" s="99" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="I10" s="99" t="inlineStr">
+        <is>
+          <t>Manual Status</t>
+        </is>
+      </c>
+      <c r="J10" s="99" t="inlineStr">
+        <is>
+          <t>Status code</t>
+        </is>
+      </c>
+      <c r="K10" s="99" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="L10" s="99" t="inlineStr">
+        <is>
+          <t>Script error</t>
+        </is>
+      </c>
+      <c r="M10" s="99" t="inlineStr">
+        <is>
+          <t>Time stamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="100" t="inlineStr">
+        <is>
+          <t>ADVANCE SEARCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Open Advanced Search in User drive</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Verify user can open advanced search panel</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Search panel is accessible</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Panel should open</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K12" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L12" s="134" t="inlineStr"/>
+      <c r="M12" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:20:03 (2.14s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC02</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Close Panel by Clicking Outside</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Verify panel closes when clicking outside</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Advanced search panel is open</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Search panel is closed</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Panel should close</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K13" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L13" s="134" t="inlineStr"/>
+      <c r="M13" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:20:08 (2.65s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Search with Type Only</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Verify search using only document type</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Files of selected type displayed</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K14" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L14" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M14" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:20:16 (5.22s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC04</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Search with Type + Attribute</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Verify attribute-based search</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Amount=5000</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Matching files displayed</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K15" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L15" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M15" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:20:24 (5.30s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC05</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Search Using Tag</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Verify tag-based filtering</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Tagged files displayed</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K16" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L16" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M16" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:20:31 (5.19s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Search Using Created Date</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Verify created date filtering</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Valid dates</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Files in range displayed</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K17" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L17" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M17" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:20:39 (5.12s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC07</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Search Using Modified Date</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Verify modified date filtering</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Valid dates</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Correct files displayed</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K18" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L18" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M18" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:20:47 (5.09s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC08</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Search Owned by Me</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Verify filtering for current user</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Only my files should be displayed. files displayed</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K19" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L19" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M19" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:20:54 (5.01s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC09</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Search Owned by Others</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Verify filtering for other users</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Other users' files displayed</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K20" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L20" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M20" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:21:02 (4.68s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Search Specific Person</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Verify search for specific user</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>user123</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Files of that user displayed</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K21" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L21" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M21" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:21:09 (4.95s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Combination Filter (Type + Tag)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Verify multiple filters together</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Invoice + Finance</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Matching files displayed</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K22" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L22" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M22" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:21:18 (6.35s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC12</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Combination Filter (All Filters)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Verify all filters together</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Advanced search completes</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Valid inputs</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Intersection data displayed</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K23" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L23" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M23" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:21:28 (7.63s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC13</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Reset Button Functionality</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Verify reset clears all filters</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Active parameters set in panel</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Parameters cleared to default</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>All filters cleared</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K24" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L24" s="134" t="inlineStr"/>
+      <c r="M24" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:21:35 (4.43s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC14</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Search with Type Attribute (Shortcut File - Shared with Me)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Verify search works for shared files only after creating shortcut</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>User A shared file with attributes to User B</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Shortcut file target resolution verified</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Type: Invoice Attribute: Amount = 7000</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Without shortcut → File should NOT appear (as per system behavior) After shortcut → File should appear in search results</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K25" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L25" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: SRCH_ADV01_TC14 | Requires a cross-user fixture: User A shares a typed file with User B, then B creates a shortcut. No second-user/share fixture exists in this single-account test env.</t>
+        </is>
+      </c>
+      <c r="M25" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:21:35 (0.00s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC15</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Search with Type Attribute (Nested Folder)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Verify search works for files stored inside nested folder structure</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Nested indexing verified</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Type: Invoice Attribute: Amount = 9000</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>File should be displayed in search results even if it is inside nested folders</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K26" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L26" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M26" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:21:44 (5.42s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC16</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Search with tag in share with other filter.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Verify system behavior, when user search with tag in Share with others</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Summary list populated</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tag Name</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>File Should be displayed</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K27" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L27" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: [UI] Could not open 'Shared With Others' context</t>
+        </is>
+      </c>
+      <c r="M27" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:21:57 (10.82s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Search with meta data in Trash</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Verify System behaviour, when user search in trash tab with meta data.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Trash records indexed</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>attribute value</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>File should be displayed</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K28" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L28" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: [UI] Could not open Trash context</t>
+        </is>
+      </c>
+      <c r="M28" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:22:11 (11.12s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC18</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Verify independent value entry in attribute fields</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Verify that each attribute field accepts its own value independently</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Input states isolated</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>A = Test1, B = Test2</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Each attribute should retain its own value</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K29" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L29" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: [DATA] Need a type with at least 2 attributes</t>
+        </is>
+      </c>
+      <c r="M29" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:22:14 (0.53s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC19</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Attribute Without Value</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Verify validation when attribute value is missing</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Validation state checked</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Select Type</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Validation message displayedORFile should be displayed</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K30" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L30" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M30" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:22:22 (5.35s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC20</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Invalid Attribute Value</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Verify invalid data handling</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Input bounds tested</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>@#$%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Proper validation or no crash</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K31" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L31" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M31" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:22:30 (5.40s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC21</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Invalid Date Range</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Verify start date greater than end date</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Date logical cross-check handled</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Date Range</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>The system should not allow the Start Date to be later than the End Date.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K32" s="137" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="L32" s="138" t="inlineStr">
+        <is>
+          <t>playwright._impl._errors.Error: Locator.fill: Error: Element is not an &lt;input&gt;, &lt;textarea&gt;, &lt;select&gt; or [contenteditable] and does not have a role allowing [aria-readonly]</t>
+        </is>
+      </c>
+      <c r="M32" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:22:36 (3.17s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC22</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Future Date Selection</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Verify future date handling</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Calendar constraints verified</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Future date</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Validation or no results</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K33" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L33" s="134" t="inlineStr"/>
+      <c r="M33" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:22:42 (3.14s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC23</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Invalid Specific Person</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Verify invalid user input</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>User tracking exception handled</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>xyz123@ios.com</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>No result / error shown</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K34" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L34" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M34" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:22:49 (4.42s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tag with No Data</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Verify unused tag behavior</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Unassigned tag checked</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>EmptyTag</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>“No results found”</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K35" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L35" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M35" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:22:57 (4.65s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>No Filter Applied</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Verify behavior when search clicked without filters</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Standard operational default checked</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Default results OR validation (as per system)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K36" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L36" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M36" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:23:02 (2.61s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC26</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Conflicting Filters</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Verify filters with no intersection</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Contradictory filtering evaluated</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Random combination</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>No results found</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K37" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L37" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M37" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:23:10 (5.86s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC27</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Large Data Stress</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Verify system behavior under heavy load</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>High file volume present in target</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Performance stability confirmed</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>System should not crash</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" s="133" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L38" s="134" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
+        </is>
+      </c>
+      <c r="M38" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:23:15 (2.55s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SRCH_ADV01_TC28</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Verify value is not applied to all attribute fields</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Verify system does not auto-fill all attributes when value is entered in one field</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Advanced search panel open</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Input isolation confirmed</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>A = Test1</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Only Attribute A should have value; other fields should remain empty</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K39" s="135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L39" s="136" t="inlineStr">
+        <is>
+          <t>Skipped: [DATA] Need a type with at least 2 attributes</t>
+        </is>
+      </c>
+      <c r="M39" s="76" t="inlineStr">
+        <is>
+          <t>2026-06-18 15:23:19 (0.54s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Total Test Cases</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Total Test Cases</t>
+        </is>
+      </c>
+      <c r="J42" s="76" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Executed Test Cases</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Executed Test Cases</t>
+        </is>
+      </c>
+      <c r="J43" s="76" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Passed Test Cases</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Passed Test Cases</t>
+        </is>
+      </c>
+      <c r="J44" s="76" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Failed Test Cases</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Failed Test Cases</t>
+        </is>
+      </c>
+      <c r="J45" s="76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Blocked Test Cases</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Blocked Test Cases</t>
+        </is>
+      </c>
+      <c r="J46" s="76" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Not Executed Test Cases</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Not Executed Test Cases</t>
+        </is>
+      </c>
+      <c r="J47" s="76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -15312,19 +17681,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="110" t="inlineStr">
+      <c r="L14" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:37:46 (4.47s)</t>
+          <t>2026-06-18 14:51:10 (4.59s)</t>
         </is>
       </c>
     </row>
@@ -15371,19 +17740,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="110" t="inlineStr">
+      <c r="L15" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:37:48 (0.87s)</t>
+          <t>2026-06-18 14:51:13 (0.90s)</t>
         </is>
       </c>
     </row>
@@ -15430,19 +17799,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="110" t="inlineStr">
+      <c r="L16" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:37:51 (0.82s)</t>
+          <t>2026-06-18 14:51:15 (0.81s)</t>
         </is>
       </c>
     </row>
@@ -15489,19 +17858,19 @@
           <t xml:space="preserve"> - </t>
         </is>
       </c>
-      <c r="K17" s="106" t="inlineStr">
+      <c r="K17" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L17" s="111" t="inlineStr">
+      <c r="L17" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Login_04 | BLOCKED: 'Remember Me' checkbox not in current UI — inspect DOM and update selector in login_page.py</t>
         </is>
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:37:52 (0.00s)</t>
+          <t>2026-06-18 14:51:17 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -15548,19 +17917,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K18" s="104" t="inlineStr">
+      <c r="K18" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L18" s="110" t="inlineStr">
+      <c r="L18" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:37:54 (2.30s)</t>
+          <t>2026-06-18 14:51:19 (2.65s)</t>
         </is>
       </c>
     </row>
@@ -15607,19 +17976,19 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="K19" s="108" t="inlineStr">
+      <c r="K19" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L19" s="112" t="inlineStr">
+      <c r="L19" s="125" t="inlineStr">
         <is>
           <t>HTTP 500 Internal Server Error | AssertionError: [API] Expected 401, got 500. Body: {"error":"Incorrect credentials","message":""}</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:38:05 (0.14s)</t>
+          <t>2026-06-18 14:51:30 (0.14s)</t>
         </is>
       </c>
     </row>
@@ -15666,19 +18035,19 @@
           <t>404 Not Found</t>
         </is>
       </c>
-      <c r="K20" s="104" t="inlineStr">
+      <c r="K20" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L20" s="110" t="inlineStr">
+      <c r="L20" s="121" t="inlineStr">
         <is>
           <t>HTTP 404 Not Found</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:38:08 (3.63s)</t>
+          <t>2026-06-18 14:51:33 (3.58s)</t>
         </is>
       </c>
     </row>
@@ -15725,19 +18094,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K21" s="104" t="inlineStr">
+      <c r="K21" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L21" s="110" t="inlineStr">
+      <c r="L21" s="121" t="inlineStr">
         <is>
           <t>HTTP 500 Internal Server Error</t>
         </is>
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:38:11 (2.63s)</t>
+          <t>2026-06-18 14:51:36 (2.60s)</t>
         </is>
       </c>
     </row>
@@ -15784,19 +18153,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K22" s="108" t="inlineStr">
+      <c r="K22" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L22" s="112" t="inlineStr">
+      <c r="L22" s="125" t="inlineStr">
         <is>
           <t>HTTP 500 Internal Server Error | AssertionError: [API] Expected 400, got 500. Body: {"error":"Incorrect credentials","message":""}</t>
         </is>
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:38:11 (0.08s)</t>
+          <t>2026-06-18 14:51:36 (0.09s)</t>
         </is>
       </c>
     </row>
@@ -15843,19 +18212,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K23" s="104" t="inlineStr">
+      <c r="K23" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L23" s="110" t="inlineStr">
+      <c r="L23" s="121" t="inlineStr">
         <is>
           <t>HTTP 500 Internal Server Error</t>
         </is>
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:38:14 (2.58s)</t>
+          <t>2026-06-18 14:51:39 (2.54s)</t>
         </is>
       </c>
     </row>
@@ -15902,19 +18271,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K24" s="104" t="inlineStr">
+      <c r="K24" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L24" s="110" t="inlineStr">
+      <c r="L24" s="121" t="inlineStr">
         <is>
           <t>HTTP 404 Not Found</t>
         </is>
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:38:16 (2.71s)</t>
+          <t>2026-06-18 14:51:41 (2.59s)</t>
         </is>
       </c>
     </row>
@@ -15961,19 +18330,19 @@
           <t>423 Locked</t>
         </is>
       </c>
-      <c r="K25" s="106" t="inlineStr">
+      <c r="K25" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L25" s="111" t="inlineStr">
+      <c r="L25" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Login_12 | BLOCKED: No locked account in test env — create one and update LOCKED_USER</t>
         </is>
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:38:16 (0.00s)</t>
+          <t>2026-06-18 14:51:41 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -16020,19 +18389,19 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="K26" s="104" t="inlineStr">
+      <c r="K26" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L26" s="110" t="inlineStr">
+      <c r="L26" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M26" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:38:20 (3.73s)</t>
+          <t>2026-06-18 14:51:45 (3.66s)</t>
         </is>
       </c>
     </row>
@@ -16079,15 +18448,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K27" s="104" t="inlineStr">
+      <c r="K27" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L27" s="110" t="inlineStr"/>
+      <c r="L27" s="121" t="inlineStr"/>
       <c r="M27" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:38:21 (0.41s)</t>
+          <t>2026-06-18 14:51:46 (0.40s)</t>
         </is>
       </c>
     </row>
@@ -16134,15 +18503,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K28" s="104" t="inlineStr">
+      <c r="K28" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L28" s="110" t="inlineStr"/>
+      <c r="L28" s="121" t="inlineStr"/>
       <c r="M28" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:38:21 (0.36s)</t>
+          <t>2026-06-18 14:51:46 (0.35s)</t>
         </is>
       </c>
     </row>
@@ -16189,15 +18558,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K29" s="104" t="inlineStr">
+      <c r="K29" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L29" s="110" t="inlineStr"/>
+      <c r="L29" s="121" t="inlineStr"/>
       <c r="M29" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:38:22 (0.36s)</t>
+          <t>2026-06-18 14:51:47 (0.32s)</t>
         </is>
       </c>
     </row>
@@ -16244,15 +18613,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K30" s="104" t="inlineStr">
+      <c r="K30" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L30" s="110" t="inlineStr"/>
+      <c r="L30" s="121" t="inlineStr"/>
       <c r="M30" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:38:23 (0.95s)</t>
+          <t>2026-06-18 14:51:47 (0.92s)</t>
         </is>
       </c>
     </row>
@@ -16299,19 +18668,19 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="K31" s="108" t="inlineStr">
+      <c r="K31" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L31" s="112" t="inlineStr">
+      <c r="L31" s="125" t="inlineStr">
         <is>
           <t>HTTP 500 Internal Server Error | AssertionError: [API] Expected 401, got 500. Body: {"error":"Incorrect credentials","message":""}</t>
         </is>
       </c>
       <c r="M31" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:38:23 (0.13s)</t>
+          <t>2026-06-18 14:51:48 (0.13s)</t>
         </is>
       </c>
     </row>
@@ -16358,19 +18727,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K32" s="104" t="inlineStr">
+      <c r="K32" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L32" s="110" t="inlineStr">
+      <c r="L32" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M32" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:38:24 (0.86s)</t>
+          <t>2026-06-18 14:51:48 (0.78s)</t>
         </is>
       </c>
     </row>
@@ -16536,12 +18905,12 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="25" defaultRowHeight="14.5"/>
   <cols>
     <col width="14.54296875" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
-    <col width="40.6328125" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="26.81640625" customWidth="1" style="1" min="2" max="2"/>
     <col width="20.54296875" bestFit="1" customWidth="1" style="41" min="3" max="3"/>
     <col width="41.6328125" bestFit="1" customWidth="1" style="41" min="4" max="4"/>
     <col width="26.36328125" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
     <col width="27.54296875" bestFit="1" customWidth="1" style="41" min="6" max="6"/>
-    <col width="45.7265625" bestFit="1" customWidth="1" style="1" min="7" max="7"/>
+    <col width="30.81640625" customWidth="1" style="1" min="7" max="7"/>
     <col width="38.90625" bestFit="1" customWidth="1" style="1" min="8" max="8"/>
     <col width="14" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
     <col width="28.1796875" bestFit="1" customWidth="1" style="1" min="10" max="10"/>
@@ -16549,8 +18918,8 @@
     <col width="47" bestFit="1" customWidth="1" style="41" min="12" max="12"/>
     <col width="26.26953125" bestFit="1" customWidth="1" style="1" min="13" max="13"/>
     <col width="25" customWidth="1" style="29" min="14" max="14"/>
-    <col width="25" customWidth="1" style="1" min="15" max="23"/>
-    <col width="25" customWidth="1" style="1" min="24" max="16384"/>
+    <col width="25" customWidth="1" style="1" min="15" max="27"/>
+    <col width="25" customWidth="1" style="1" min="28" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.5" customHeight="1" s="29">
@@ -16769,19 +19138,19 @@
 200 OK</t>
         </is>
       </c>
-      <c r="K12" s="104" t="inlineStr">
+      <c r="K12" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="113" t="inlineStr">
+      <c r="L12" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:38:46 (8.05s)</t>
+          <t>2026-06-18 14:52:10 (8.03s)</t>
         </is>
       </c>
       <c r="N12" s="11" t="n"/>
@@ -16834,19 +19203,19 @@
 200 OK</t>
         </is>
       </c>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="113" t="inlineStr">
+      <c r="L13" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:39:03 (16.80s)</t>
+          <t>2026-06-18 14:52:18 (7.98s)</t>
         </is>
       </c>
       <c r="N13" s="11" t="n"/>
@@ -16899,19 +19268,19 @@
 200 OK</t>
         </is>
       </c>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="113" t="inlineStr">
+      <c r="L14" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:39:11 (7.99s)</t>
+          <t>2026-06-18 14:52:26 (7.96s)</t>
         </is>
       </c>
       <c r="N14" s="11" t="n"/>
@@ -16964,19 +19333,19 @@
 200 OK</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="113" t="inlineStr">
+      <c r="L15" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:39:19 (7.92s)</t>
+          <t>2026-06-18 14:52:34 (8.01s)</t>
         </is>
       </c>
       <c r="N15" s="11" t="n"/>
@@ -17029,19 +19398,19 @@
 200 OK</t>
         </is>
       </c>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="113" t="inlineStr">
+      <c r="L16" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:39:27 (8.00s)</t>
+          <t>2026-06-18 14:52:42 (7.91s)</t>
         </is>
       </c>
       <c r="N16" s="11" t="n"/>
@@ -17089,19 +19458,19 @@
           <t>If fails → Upload failed. Please try again</t>
         </is>
       </c>
-      <c r="K17" s="104" t="inlineStr">
+      <c r="K17" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L17" s="113" t="inlineStr">
+      <c r="L17" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:39:43 (16.90s)</t>
+          <t>2026-06-18 14:52:59 (17.07s)</t>
         </is>
       </c>
       <c r="N17" s="11" t="n"/>
@@ -17149,19 +19518,19 @@
           <t>If rejected → "File size exceeds limit" (incorrect behavior)</t>
         </is>
       </c>
-      <c r="K18" s="104" t="inlineStr">
+      <c r="K18" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L18" s="113" t="inlineStr">
+      <c r="L18" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:40:43 (59.26s)</t>
+          <t>2026-06-18 14:54:07 (67.90s)</t>
         </is>
       </c>
       <c r="N18" s="11" t="n"/>
@@ -17209,19 +19578,19 @@
           <t>If 0 KB → "File is empty"</t>
         </is>
       </c>
-      <c r="K19" s="104" t="inlineStr">
+      <c r="K19" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L19" s="113" t="inlineStr">
+      <c r="L19" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:40:51 (8.05s)</t>
+          <t>2026-06-18 14:54:15 (8.01s)</t>
         </is>
       </c>
       <c r="N19" s="11" t="n"/>
@@ -17269,19 +19638,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K20" s="104" t="inlineStr">
+      <c r="K20" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L20" s="113" t="inlineStr">
+      <c r="L20" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:41:08 (16.92s)</t>
+          <t>2026-06-18 14:54:32 (16.79s)</t>
         </is>
       </c>
       <c r="N20" s="11" t="n"/>
@@ -17329,19 +19698,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K21" s="104" t="inlineStr">
+      <c r="K21" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L21" s="113" t="inlineStr">
+      <c r="L21" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:41:25 (16.94s)</t>
+          <t>2026-06-18 14:54:49 (16.86s)</t>
         </is>
       </c>
       <c r="N21" s="11" t="n"/>
@@ -17389,19 +19758,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K22" s="104" t="inlineStr">
+      <c r="K22" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L22" s="113" t="inlineStr">
+      <c r="L22" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:41:42 (17.12s)</t>
+          <t>2026-06-18 14:55:06 (17.09s)</t>
         </is>
       </c>
       <c r="N22" s="11" t="n"/>
@@ -17449,19 +19818,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K23" s="106" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="L23" s="115" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK | Skipped: [UI→API] Could not capture open response: Timeout 15000ms exceeded while waiting for event "response"</t>
+      <c r="K23" s="120" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L23" s="126" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:42:14 (31.95s)</t>
+          <t>2026-06-18 14:55:24 (17.59s)</t>
         </is>
       </c>
       <c r="N23" s="11" t="n"/>
@@ -17509,24 +19878,24 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K24" s="106" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="L24" s="115" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK | Skipped: [UI] Could not find/select uploaded file 'India_Overview.docx' in manager</t>
+      <c r="K24" s="120" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L24" s="126" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:42:39 (24.88s)</t>
+          <t>2026-06-18 14:56:14 (49.97s)</t>
         </is>
       </c>
       <c r="N24" s="11" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="29" customHeight="1" s="29">
       <c r="A25" s="72" t="n"/>
       <c r="B25" s="72" t="inlineStr">
         <is>
@@ -17569,19 +19938,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K25" s="106" t="inlineStr">
+      <c r="K25" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L25" s="115" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK | Skipped: [UI] Could not find row for 'test.docx' in file manager</t>
+      <c r="L25" s="128" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK | Skipped: [UI→API] Could not capture delete response: Timeout 15000ms exceeded while waiting for event "response"</t>
         </is>
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:43:06 (26.90s)</t>
+          <t>2026-06-18 14:56:46 (32.48s)</t>
         </is>
       </c>
       <c r="N25" s="11" t="n"/>
@@ -17629,19 +19998,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K26" s="104" t="inlineStr">
+      <c r="K26" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L26" s="113" t="inlineStr">
+      <c r="L26" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M26" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:43:25 (18.64s)</t>
+          <t>2026-06-18 14:57:05 (18.63s)</t>
         </is>
       </c>
       <c r="N26" s="11" t="n"/>
@@ -17689,19 +20058,19 @@
           <t>400 Bad Request/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K27" s="104" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="L27" s="113" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK</t>
+      <c r="K27" s="124" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="L27" s="127" t="inlineStr">
+        <is>
+          <t>HTTP 500 Internal Server Error | AssertionError: [API] Expected 200 for 480 MB file (within 500 MB limit), got 500. Body: {"error":"Handler dispatch failed; nested exception is java.lang.OutOfMemoryError: Cannot reserve 501924886 bytes of direct buffer memory (allocated: 1525091435, limit: 1556938752)","serviceName":"DMS</t>
         </is>
       </c>
       <c r="M27" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:44:34 (68.89s)</t>
+          <t>2026-06-18 14:58:04 (59.01s)</t>
         </is>
       </c>
       <c r="N27" s="11" t="n"/>
@@ -17749,19 +20118,19 @@
           <t>415 Unsupported Media Type/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K28" s="104" t="inlineStr">
+      <c r="K28" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L28" s="113" t="inlineStr">
+      <c r="L28" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M28" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:44:36 (1.87s)</t>
+          <t>2026-06-18 14:58:06 (1.87s)</t>
         </is>
       </c>
       <c r="N28" s="11" t="n"/>
@@ -17809,19 +20178,19 @@
           <t>400 Bad Request/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K29" s="104" t="inlineStr">
+      <c r="K29" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L29" s="113" t="inlineStr">
+      <c r="L29" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M29" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:44:36 (0.24s)</t>
+          <t>2026-06-18 14:58:06 (0.20s)</t>
         </is>
       </c>
       <c r="N29" s="11" t="n"/>
@@ -17869,15 +20238,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K30" s="104" t="inlineStr">
+      <c r="K30" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L30" s="113" t="inlineStr"/>
+      <c r="L30" s="126" t="inlineStr"/>
       <c r="M30" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:44:47 (11.15s)</t>
+          <t>2026-06-18 14:58:16 (9.66s)</t>
         </is>
       </c>
       <c r="N30" s="11" t="n"/>
@@ -17925,19 +20294,19 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K31" s="108" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="L31" s="114" t="inlineStr">
-        <is>
-          <t>HTTP 500 Internal Server Error | AssertionError: [API] Expected 200 for action='replace', got 500. Body: {"error":"Handler dispatch failed; nested exception is java.lang.OutOfMemoryError: Cannot reserve 501924886 bytes of direct buffer memory (allocated: 1513536767, limit: 1556938752)","serviceName":"DMS</t>
+      <c r="K31" s="120" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L31" s="126" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M31" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:45:44 (56.71s)</t>
+          <t>2026-06-18 14:59:20 (64.03s)</t>
         </is>
       </c>
       <c r="N31" s="11" t="n"/>
@@ -17985,19 +20354,19 @@
           <t>415 Unsupported Media Type</t>
         </is>
       </c>
-      <c r="K32" s="106" t="inlineStr">
+      <c r="K32" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L32" s="115" t="inlineStr">
+      <c r="L32" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_21 | BLOCKED: Preview selector unknown</t>
         </is>
       </c>
       <c r="M32" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:45:44 (0.00s)</t>
+          <t>2026-06-18 14:59:20 (0.00s)</t>
         </is>
       </c>
       <c r="N32" s="11" t="n"/>
@@ -18045,19 +20414,19 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K33" s="106" t="inlineStr">
+      <c r="K33" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L33" s="115" t="inlineStr">
+      <c r="L33" s="128" t="inlineStr">
         <is>
           <t>HTTP 200 OK | Skipped: [UI] No test*.docx row found in file manager</t>
         </is>
       </c>
       <c r="M33" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:01 (16.86s)</t>
+          <t>2026-06-18 14:59:37 (17.04s)</t>
         </is>
       </c>
       <c r="N33" s="11" t="n"/>
@@ -18105,19 +20474,19 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K34" s="106" t="inlineStr">
+      <c r="K34" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L34" s="115" t="inlineStr">
+      <c r="L34" s="128" t="inlineStr">
         <is>
           <t>HTTP 200 OK | Skipped: [UI] No test*.docx row found in file manager</t>
         </is>
       </c>
       <c r="M34" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:18 (16.92s)</t>
+          <t>2026-06-18 14:59:54 (16.82s)</t>
         </is>
       </c>
       <c r="N34" s="11" t="n"/>
@@ -18165,19 +20534,19 @@
           <t>401 Unauthorized</t>
         </is>
       </c>
-      <c r="K35" s="104" t="inlineStr">
+      <c r="K35" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L35" s="113" t="inlineStr">
+      <c r="L35" s="126" t="inlineStr">
         <is>
           <t>HTTP 401 Unauthorized</t>
         </is>
       </c>
       <c r="M35" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:18 (0.04s)</t>
+          <t>2026-06-18 14:59:54 (0.03s)</t>
         </is>
       </c>
       <c r="N35" s="11" t="n"/>
@@ -18225,19 +20594,19 @@
           <t>408 Request Timeout</t>
         </is>
       </c>
-      <c r="K36" s="104" t="inlineStr">
+      <c r="K36" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L36" s="113" t="inlineStr">
+      <c r="L36" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M36" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:38 (20.02s)</t>
+          <t>2026-06-18 15:00:14 (19.93s)</t>
         </is>
       </c>
       <c r="N36" s="11" t="n"/>
@@ -18285,19 +20654,19 @@
           <t>Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K37" s="104" t="inlineStr">
+      <c r="K37" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L37" s="113" t="inlineStr">
+      <c r="L37" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M37" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:40 (1.74s)</t>
+          <t>2026-06-18 15:00:16 (1.76s)</t>
         </is>
       </c>
       <c r="N37" s="11" t="n"/>
@@ -18345,19 +20714,19 @@
           <t>Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K38" s="104" t="inlineStr">
+      <c r="K38" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L38" s="113" t="inlineStr">
+      <c r="L38" s="126" t="inlineStr">
         <is>
           <t>HTTP 403 Forbidden</t>
         </is>
       </c>
       <c r="M38" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:40 (0.23s)</t>
+          <t>2026-06-18 15:00:16 (0.21s)</t>
         </is>
       </c>
       <c r="N38" s="11" t="n"/>
@@ -18405,19 +20774,19 @@
           <t>415 Unsupported Media Type</t>
         </is>
       </c>
-      <c r="K39" s="104" t="inlineStr">
+      <c r="K39" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L39" s="113" t="inlineStr">
+      <c r="L39" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M39" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:41 (0.23s)</t>
+          <t>2026-06-18 15:00:17 (0.21s)</t>
         </is>
       </c>
       <c r="N39" s="11" t="n"/>
@@ -18465,19 +20834,19 @@
           <t xml:space="preserve"> Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K40" s="104" t="inlineStr">
+      <c r="K40" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L40" s="113" t="inlineStr">
+      <c r="L40" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M40" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:41 (0.21s)</t>
+          <t>2026-06-18 15:00:17 (0.24s)</t>
         </is>
       </c>
       <c r="N40" s="11" t="n"/>
@@ -18525,19 +20894,19 @@
           <t>Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K41" s="104" t="inlineStr">
+      <c r="K41" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L41" s="113" t="inlineStr">
+      <c r="L41" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M41" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:41 (0.21s)</t>
+          <t>2026-06-18 15:00:17 (0.23s)</t>
         </is>
       </c>
       <c r="N41" s="11" t="n"/>
@@ -18586,19 +20955,19 @@
 </t>
         </is>
       </c>
-      <c r="K42" s="104" t="inlineStr">
+      <c r="K42" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L42" s="113" t="inlineStr">
+      <c r="L42" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M42" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:42 (0.24s)</t>
+          <t>2026-06-18 15:00:18 (0.21s)</t>
         </is>
       </c>
       <c r="N42" s="11" t="n"/>
@@ -18646,19 +21015,19 @@
           <t>/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K43" s="104" t="inlineStr">
+      <c r="K43" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L43" s="113" t="inlineStr">
+      <c r="L43" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M43" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:44 (2.34s)</t>
+          <t>2026-06-18 15:00:20 (1.68s)</t>
         </is>
       </c>
       <c r="N43" s="11" t="n"/>
@@ -18706,19 +21075,19 @@
           <t>Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K44" s="104" t="inlineStr">
+      <c r="K44" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L44" s="113" t="inlineStr">
+      <c r="L44" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M44" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:46 (1.69s)</t>
+          <t>2026-06-18 15:00:21 (1.69s)</t>
         </is>
       </c>
       <c r="N44" s="11" t="n"/>
@@ -18766,19 +21135,19 @@
           <t>Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K45" s="106" t="inlineStr">
+      <c r="K45" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L45" s="115" t="inlineStr">
+      <c r="L45" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_34 | BLOCKED: Requires custom MIME header crafting</t>
         </is>
       </c>
       <c r="M45" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:46 (0.00s)</t>
+          <t>2026-06-18 15:00:21 (0.00s)</t>
         </is>
       </c>
       <c r="N45" s="11" t="n"/>
@@ -18826,19 +21195,19 @@
           <t>415 Unsupported Media Type</t>
         </is>
       </c>
-      <c r="K46" s="106" t="inlineStr">
+      <c r="K46" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L46" s="115" t="inlineStr">
+      <c r="L46" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_35 | BLOCKED: Need an encrypted test file</t>
         </is>
       </c>
       <c r="M46" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:46 (0.00s)</t>
+          <t>2026-06-18 15:00:21 (0.00s)</t>
         </is>
       </c>
       <c r="N46" s="11" t="n"/>
@@ -18886,19 +21255,19 @@
           <t>415 Unsupported Media Type</t>
         </is>
       </c>
-      <c r="K47" s="106" t="inlineStr">
+      <c r="K47" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L47" s="115" t="inlineStr">
+      <c r="L47" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_36 | BLOCKED: Need a password-protected PDF</t>
         </is>
       </c>
       <c r="M47" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:46 (0.00s)</t>
+          <t>2026-06-18 15:00:21 (0.00s)</t>
         </is>
       </c>
       <c r="N47" s="11" t="n"/>
@@ -18946,19 +21315,19 @@
           <t>200 OK / 415 Unsupported Media Type</t>
         </is>
       </c>
-      <c r="K48" s="104" t="inlineStr">
+      <c r="K48" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L48" s="113" t="inlineStr">
+      <c r="L48" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M48" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:47 (0.40s)</t>
+          <t>2026-06-18 15:00:22 (0.39s)</t>
         </is>
       </c>
       <c r="N48" s="11" t="n"/>
@@ -19006,19 +21375,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K49" s="106" t="inlineStr">
+      <c r="K49" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L49" s="115" t="inlineStr">
+      <c r="L49" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_38 | BLOCKED: Need a nested ZIP test file</t>
         </is>
       </c>
       <c r="M49" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:47 (0.00s)</t>
+          <t>2026-06-18 15:00:22 (0.00s)</t>
         </is>
       </c>
       <c r="N49" s="11" t="n"/>
@@ -19066,19 +21435,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K50" s="104" t="inlineStr">
+      <c r="K50" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L50" s="113" t="inlineStr">
+      <c r="L50" s="126" t="inlineStr">
         <is>
           <t>HTTP 403 Forbidden</t>
         </is>
       </c>
       <c r="M50" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:47 (0.20s)</t>
+          <t>2026-06-18 15:00:22 (0.21s)</t>
         </is>
       </c>
       <c r="N50" s="11" t="n"/>
@@ -19126,19 +21495,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K51" s="104" t="inlineStr">
+      <c r="K51" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L51" s="113" t="inlineStr">
+      <c r="L51" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M51" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:48 (0.40s)</t>
+          <t>2026-06-18 15:00:23 (0.43s)</t>
         </is>
       </c>
       <c r="N51" s="11" t="n"/>
@@ -19186,19 +21555,19 @@
           <t>400 Bad Request/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K52" s="106" t="inlineStr">
+      <c r="K52" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L52" s="115" t="inlineStr">
+      <c r="L52" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_41 | BLOCKED: Size limit unknown</t>
         </is>
       </c>
       <c r="M52" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:48 (0.00s)</t>
+          <t>2026-06-18 15:00:23 (0.00s)</t>
         </is>
       </c>
       <c r="N52" s="11" t="n"/>
@@ -19246,19 +21615,19 @@
           <t>400 Bad Request/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K53" s="106" t="inlineStr">
+      <c r="K53" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L53" s="115" t="inlineStr">
+      <c r="L53" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_42 | BLOCKED: Size limit unknown</t>
         </is>
       </c>
       <c r="M53" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:48 (0.00s)</t>
+          <t>2026-06-18 15:00:23 (0.00s)</t>
         </is>
       </c>
       <c r="N53" s="11" t="n"/>
@@ -19306,19 +21675,19 @@
           <t>413 Payload Too Large/Error Handeld by Frontend</t>
         </is>
       </c>
-      <c r="K54" s="106" t="inlineStr">
+      <c r="K54" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L54" s="115" t="inlineStr">
+      <c r="L54" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_43 | BLOCKED: Creating very large files in CI is risky — run manually</t>
         </is>
       </c>
       <c r="M54" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:48 (0.00s)</t>
+          <t>2026-06-18 15:00:23 (0.00s)</t>
         </is>
       </c>
       <c r="N54" s="11" t="n"/>
@@ -19366,19 +21735,19 @@
           <t>400 Bad Request/415 Unsupported Media Type</t>
         </is>
       </c>
-      <c r="K55" s="104" t="inlineStr">
+      <c r="K55" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L55" s="113" t="inlineStr">
+      <c r="L55" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M55" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:48 (0.25s)</t>
+          <t>2026-06-18 15:00:23 (0.20s)</t>
         </is>
       </c>
       <c r="N55" s="11" t="n"/>
@@ -19426,19 +21795,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K56" s="106" t="inlineStr">
+      <c r="K56" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L56" s="115" t="inlineStr">
+      <c r="L56" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_45 | BLOCKED: Size limit unknown</t>
         </is>
       </c>
       <c r="M56" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:48 (0.00s)</t>
+          <t>2026-06-18 15:00:23 (0.00s)</t>
         </is>
       </c>
       <c r="N56" s="11" t="n"/>
@@ -19486,19 +21855,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K57" s="106" t="inlineStr">
+      <c r="K57" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L57" s="115" t="inlineStr">
+      <c r="L57" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_46 | BLOCKED: Cannot simulate slow network in automated test</t>
         </is>
       </c>
       <c r="M57" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:46:48 (0.00s)</t>
+          <t>2026-06-18 15:00:23 (0.00s)</t>
         </is>
       </c>
       <c r="N57" s="11" t="n"/>
@@ -19546,19 +21915,19 @@
           <t>408 Request Timeout</t>
         </is>
       </c>
-      <c r="K58" s="104" t="inlineStr">
+      <c r="K58" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L58" s="113" t="inlineStr">
+      <c r="L58" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M58" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:47:08 (19.89s)</t>
+          <t>2026-06-18 15:00:43 (19.90s)</t>
         </is>
       </c>
       <c r="N58" s="11" t="n"/>
@@ -19606,19 +21975,19 @@
           <t>408 Request Timeout</t>
         </is>
       </c>
-      <c r="K59" s="104" t="inlineStr">
+      <c r="K59" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L59" s="113" t="inlineStr">
+      <c r="L59" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M59" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:47:28 (19.88s)</t>
+          <t>2026-06-18 15:01:03 (19.90s)</t>
         </is>
       </c>
       <c r="N59" s="11" t="n"/>
@@ -19666,19 +22035,19 @@
           <t>Uplaod Successfully</t>
         </is>
       </c>
-      <c r="K60" s="106" t="inlineStr">
+      <c r="K60" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L60" s="115" t="inlineStr">
+      <c r="L60" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_49 | KNOWN FAIL: Excel marks as FAIL — IMIR does not support resume upload</t>
         </is>
       </c>
       <c r="M60" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:47:28 (0.00s)</t>
+          <t>2026-06-18 15:01:03 (0.00s)</t>
         </is>
       </c>
       <c r="N60" s="11" t="n"/>
@@ -19726,19 +22095,19 @@
           <t>200/400</t>
         </is>
       </c>
-      <c r="K61" s="104" t="inlineStr">
+      <c r="K61" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L61" s="116" t="inlineStr">
+      <c r="L61" s="129" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M61" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:47:28 (0.48s)</t>
+          <t>2026-06-18 15:01:04 (0.45s)</t>
         </is>
       </c>
       <c r="N61" s="11" t="n"/>
@@ -19786,19 +22155,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K62" s="104" t="inlineStr">
+      <c r="K62" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L62" s="113" t="inlineStr">
+      <c r="L62" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M62" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:47:29 (0.43s)</t>
+          <t>2026-06-18 15:01:04 (0.40s)</t>
         </is>
       </c>
       <c r="N62" s="11" t="n"/>
@@ -19846,19 +22215,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K63" s="104" t="inlineStr">
+      <c r="K63" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L63" s="113" t="inlineStr">
+      <c r="L63" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M63" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:47:29 (0.24s)</t>
+          <t>2026-06-18 15:01:05 (0.25s)</t>
         </is>
       </c>
       <c r="N63" s="11" t="n"/>
@@ -19906,19 +22275,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K64" s="104" t="inlineStr">
+      <c r="K64" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L64" s="113" t="inlineStr">
+      <c r="L64" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M64" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:47:30 (0.42s)</t>
+          <t>2026-06-18 15:01:05 (0.43s)</t>
         </is>
       </c>
       <c r="N64" s="11" t="n"/>
@@ -19966,19 +22335,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K65" s="104" t="inlineStr">
+      <c r="K65" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L65" s="113" t="inlineStr">
+      <c r="L65" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M65" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:47:31 (0.43s)</t>
+          <t>2026-06-18 15:01:06 (0.41s)</t>
         </is>
       </c>
       <c r="N65" s="11" t="n"/>
@@ -20026,19 +22395,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K66" s="104" t="inlineStr">
+      <c r="K66" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L66" s="113" t="inlineStr">
+      <c r="L66" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M66" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:47:31 (0.41s)</t>
+          <t>2026-06-18 15:01:06 (0.45s)</t>
         </is>
       </c>
       <c r="N66" s="11" t="n"/>
@@ -20086,19 +22455,19 @@
           <t>409 Conflict</t>
         </is>
       </c>
-      <c r="K67" s="104" t="inlineStr">
+      <c r="K67" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L67" s="113" t="inlineStr">
+      <c r="L67" s="126" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request</t>
         </is>
       </c>
       <c r="M67" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:47:32 (0.66s)</t>
+          <t>2026-06-18 15:01:07 (0.74s)</t>
         </is>
       </c>
       <c r="N67" s="11" t="n"/>
@@ -20146,15 +22515,15 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K68" s="104" t="inlineStr">
+      <c r="K68" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L68" s="113" t="inlineStr"/>
+      <c r="L68" s="126" t="inlineStr"/>
       <c r="M68" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:47:32 (0.01s)</t>
+          <t>2026-06-18 15:01:07 (0.02s)</t>
         </is>
       </c>
       <c r="N68" s="11" t="n"/>
@@ -20202,19 +22571,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K69" s="106" t="inlineStr">
+      <c r="K69" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L69" s="115" t="inlineStr">
+      <c r="L69" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_58 | KNOWN FAIL: Excel marks as FAIL — drag-and-drop returns 400, document as known bug</t>
         </is>
       </c>
       <c r="M69" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:47:32 (0.00s)</t>
+          <t>2026-06-18 15:01:07 (0.00s)</t>
         </is>
       </c>
       <c r="N69" s="11" t="n"/>
@@ -20262,19 +22631,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K70" s="106" t="inlineStr">
+      <c r="K70" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L70" s="115" t="inlineStr">
+      <c r="L70" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_59 | BLOCKED: Progress bar selector unknown — inspect upload dialog HTML</t>
         </is>
       </c>
       <c r="M70" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:47:32 (0.00s)</t>
+          <t>2026-06-18 15:01:07 (0.00s)</t>
         </is>
       </c>
       <c r="N70" s="11" t="n"/>
@@ -20322,15 +22691,15 @@
           <t>Canceled (client-side)</t>
         </is>
       </c>
-      <c r="K71" s="104" t="inlineStr">
+      <c r="K71" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L71" s="113" t="inlineStr"/>
+      <c r="L71" s="126" t="inlineStr"/>
       <c r="M71" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:47:34 (2.58s)</t>
+          <t>2026-06-18 15:01:10 (2.48s)</t>
         </is>
       </c>
       <c r="N71" s="11" t="n"/>
@@ -20378,19 +22747,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K72" s="106" t="inlineStr">
+      <c r="K72" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L72" s="115" t="inlineStr">
+      <c r="L72" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_61 | BLOCKED: Retry UI not identified</t>
         </is>
       </c>
       <c r="M72" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:47:34 (0.00s)</t>
+          <t>2026-06-18 15:01:10 (0.00s)</t>
         </is>
       </c>
       <c r="N72" s="11" t="n"/>
@@ -20438,19 +22807,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K73" s="104" t="inlineStr">
+      <c r="K73" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L73" s="113" t="inlineStr">
+      <c r="L73" s="126" t="inlineStr">
         <is>
           <t>HTTP 415 Unsupported Media Type</t>
         </is>
       </c>
       <c r="M73" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:47:36 (1.77s)</t>
+          <t>2026-06-18 15:01:11 (1.62s)</t>
         </is>
       </c>
       <c r="N73" s="11" t="n"/>
@@ -20498,19 +22867,19 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K74" s="104" t="inlineStr">
+      <c r="K74" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L74" s="113" t="inlineStr">
+      <c r="L74" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M74" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:47:56 (19.85s)</t>
+          <t>2026-06-18 15:01:31 (19.86s)</t>
         </is>
       </c>
       <c r="N74" s="11" t="n"/>
@@ -20558,19 +22927,19 @@
           <t>408 Request Timeout</t>
         </is>
       </c>
-      <c r="K75" s="104" t="inlineStr">
+      <c r="K75" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L75" s="113" t="inlineStr">
+      <c r="L75" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M75" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:48:16 (20.00s)</t>
+          <t>2026-06-18 15:01:51 (19.90s)</t>
         </is>
       </c>
       <c r="N75" s="11" t="n"/>
@@ -20618,19 +22987,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K76" s="104" t="inlineStr">
+      <c r="K76" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L76" s="113" t="inlineStr">
+      <c r="L76" s="126" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M76" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:48:43 (26.90s)</t>
+          <t>2026-06-18 15:02:18 (26.93s)</t>
         </is>
       </c>
       <c r="N76" s="11" t="n"/>
@@ -20678,19 +23047,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K77" s="106" t="inlineStr">
+      <c r="K77" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L77" s="115" t="inlineStr">
+      <c r="L77" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_66 | BLOCKED: Metadata API endpoint unknown</t>
         </is>
       </c>
       <c r="M77" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:48:43 (0.00s)</t>
+          <t>2026-06-18 15:02:18 (0.00s)</t>
         </is>
       </c>
       <c r="N77" s="11" t="n"/>
@@ -20738,19 +23107,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K78" s="106" t="inlineStr">
+      <c r="K78" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L78" s="115" t="inlineStr">
+      <c r="L78" s="128" t="inlineStr">
         <is>
           <t>Skipped: TC_UpLoad_67 | BLOCKED: Delete flow belongs to Delete module</t>
         </is>
       </c>
       <c r="M78" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:48:43 (0.00s)</t>
+          <t>2026-06-18 15:02:18 (0.00s)</t>
         </is>
       </c>
       <c r="N78" s="11" t="n"/>
@@ -20798,7 +23167,7 @@
         </is>
       </c>
       <c r="K82" s="75" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="83">
@@ -20816,7 +23185,7 @@
         </is>
       </c>
       <c r="K83" s="75" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84">
@@ -20852,7 +23221,7 @@
         </is>
       </c>
       <c r="K85" s="75" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" ht="29" customHeight="1" s="29">
@@ -21131,19 +23500,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K8" s="108" t="inlineStr">
+      <c r="K8" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L8" s="112" t="inlineStr">
-        <is>
-          <t>AssertionError: [UI] Source file cpf_4fecd176.docx not in grid</t>
+      <c r="L8" s="125" t="inlineStr">
+        <is>
+          <t>AssertionError: [UI] Source file cpf_721691f8.docx not in grid</t>
         </is>
       </c>
       <c r="M8" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 16:55:22 (3.42s)</t>
+          <t>2026-06-18 15:07:49 (3.33s)</t>
         </is>
       </c>
       <c r="N8" s="84" t="n"/>
@@ -21196,19 +23565,19 @@
           <t>fail</t>
         </is>
       </c>
-      <c r="K9" s="104" t="inlineStr">
+      <c r="K9" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L9" s="110" t="inlineStr">
+      <c r="L9" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M9" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 16:55:24 (1.58s)</t>
+          <t>2026-06-18 15:07:51 (1.52s)</t>
         </is>
       </c>
       <c r="N9" s="84" t="n"/>
@@ -21261,19 +23630,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K10" s="104" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="L10" s="110" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK</t>
+      <c r="K10" s="122" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="L10" s="123" t="inlineStr">
+        <is>
+          <t>Skipped: [SEED] No fixture files were available</t>
         </is>
       </c>
       <c r="M10" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 16:55:27 (2.82s)</t>
+          <t>2026-06-18 15:07:51 (0.60s)</t>
         </is>
       </c>
       <c r="N10" s="84" t="n"/>
@@ -21327,19 +23696,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K11" s="106" t="inlineStr">
+      <c r="K11" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L11" s="111" t="inlineStr">
+      <c r="L11" s="123" t="inlineStr">
         <is>
           <t>HTTP 200 OK | Skipped: [API] Download not 200 (src=400, dup=400)</t>
         </is>
       </c>
       <c r="M11" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 16:55:29 (1.81s)</t>
+          <t>2026-06-18 15:07:53 (1.84s)</t>
         </is>
       </c>
       <c r="N11" s="84" t="n"/>
@@ -21392,19 +23761,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K12" s="104" t="inlineStr">
+      <c r="K12" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="110" t="inlineStr">
+      <c r="L12" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M12" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 16:55:30 (1.54s)</t>
+          <t>2026-06-18 15:07:55 (1.49s)</t>
         </is>
       </c>
       <c r="N12" s="84" t="n"/>
@@ -21458,19 +23827,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="110" t="inlineStr">
+      <c r="L13" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M13" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 16:55:33 (3.03s)</t>
+          <t>2026-06-18 15:07:57 (2.90s)</t>
         </is>
       </c>
       <c r="N13" s="84" t="n"/>
@@ -21524,19 +23893,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="110" t="inlineStr">
+      <c r="L14" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M14" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 16:55:35 (1.93s)</t>
+          <t>2026-06-18 15:07:59 (1.86s)</t>
         </is>
       </c>
       <c r="N14" s="84" t="n"/>
@@ -21590,19 +23959,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="110" t="inlineStr">
+      <c r="L15" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 16:55:37 (1.68s)</t>
+          <t>2026-06-18 15:08:01 (1.74s)</t>
         </is>
       </c>
       <c r="N15" s="84" t="n"/>
@@ -21656,19 +24025,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="110" t="inlineStr">
+      <c r="L16" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M16" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 16:55:38 (1.09s)</t>
+          <t>2026-06-18 15:08:02 (0.90s)</t>
         </is>
       </c>
       <c r="N16" s="84" t="n"/>
@@ -21721,19 +24090,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K17" s="106" t="inlineStr">
+      <c r="K17" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L17" s="111" t="inlineStr">
+      <c r="L17" s="123" t="inlineStr">
         <is>
           <t>Skipped: Skipped per project decision — Syncfusion grid keyboard shortcut needs focus management not worth the complexity</t>
         </is>
       </c>
       <c r="M17" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 16:55:38 (0.00s)</t>
+          <t>2026-06-18 15:08:02 (0.00s)</t>
         </is>
       </c>
       <c r="N17" s="84" t="n"/>
@@ -21785,19 +24154,19 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K18" s="106" t="inlineStr">
+      <c r="K18" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L18" s="111" t="inlineStr">
+      <c r="L18" s="123" t="inlineStr">
         <is>
           <t>Skipped: [SEED] Upload status 403 | body: {"error":"File type not allowed. Please contact the admin to allow this extension.","status":"FORBIDDEN"}</t>
         </is>
       </c>
       <c r="M18" s="90" t="inlineStr">
         <is>
-          <t>2026-06-11 16:58:40 (181.60s)</t>
+          <t>2026-06-18 15:10:41 (159.39s)</t>
         </is>
       </c>
       <c r="N18" s="84" t="n"/>
@@ -21845,7 +24214,7 @@
         </is>
       </c>
       <c r="L23" s="77" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" ht="31" customHeight="1" s="29">
@@ -21861,7 +24230,7 @@
         </is>
       </c>
       <c r="L24" s="77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" ht="31" customHeight="1" s="29">
@@ -21893,7 +24262,7 @@
         </is>
       </c>
       <c r="L26" s="77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" ht="46.5" customHeight="1" s="29">
@@ -22160,19 +24529,19 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K12" s="108" t="inlineStr">
+      <c r="K12" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L12" s="112" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK | AssertionError: [UI] Folder 'ui_c0821579' did not appear in the file manager</t>
+      <c r="L12" s="125" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK | AssertionError: [UI] Folder 'ui_f28f37d2' did not appear in the file manager</t>
         </is>
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:10 (21.27s)</t>
+          <t>2026-06-18 15:03:40 (21.15s)</t>
         </is>
       </c>
     </row>
@@ -22219,19 +24588,19 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="110" t="inlineStr">
+      <c r="L13" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:10 (0.27s)</t>
+          <t>2026-06-18 15:03:41 (0.35s)</t>
         </is>
       </c>
     </row>
@@ -22278,19 +24647,19 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="110" t="inlineStr">
+      <c r="L14" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:11 (0.94s)</t>
+          <t>2026-06-18 15:03:42 (0.85s)</t>
         </is>
       </c>
     </row>
@@ -22337,19 +24706,19 @@
           <t>Handel from frontend.</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="110" t="inlineStr">
+      <c r="L15" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:12 (0.30s)</t>
+          <t>2026-06-18 15:03:42 (0.26s)</t>
         </is>
       </c>
     </row>
@@ -22396,19 +24765,19 @@
           <t>409 Conflict</t>
         </is>
       </c>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="110" t="inlineStr">
+      <c r="L16" s="121" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request</t>
         </is>
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:12 (0.60s)</t>
+          <t>2026-06-18 15:03:43 (0.53s)</t>
         </is>
       </c>
     </row>
@@ -22455,19 +24824,19 @@
           <t>Handel from frontend(Folder name cannot be empty or just spaces)</t>
         </is>
       </c>
-      <c r="K17" s="104" t="inlineStr">
+      <c r="K17" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L17" s="110" t="inlineStr">
-        <is>
-          <t>HTTP 400 Bad Request</t>
+      <c r="L17" s="121" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:16 (3.23s)</t>
+          <t>2026-06-18 15:03:46 (3.09s)</t>
         </is>
       </c>
     </row>
@@ -22514,19 +24883,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K18" s="104" t="inlineStr">
+      <c r="K18" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L18" s="110" t="inlineStr">
+      <c r="L18" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:16 (0.28s)</t>
+          <t>2026-06-18 15:03:47 (0.27s)</t>
         </is>
       </c>
     </row>
@@ -22573,19 +24942,19 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K19" s="106" t="inlineStr">
+      <c r="K19" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L19" s="111" t="inlineStr">
+      <c r="L19" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_08 | BLOCKED: Cannot reliably trigger 500 from a client test — requires server-side fault injection</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:16 (0.00s)</t>
+          <t>2026-06-18 15:03:47 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -22632,19 +25001,19 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K20" s="104" t="inlineStr">
+      <c r="K20" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L20" s="110" t="inlineStr">
+      <c r="L20" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:24 (7.89s)</t>
+          <t>2026-06-18 15:03:55 (7.88s)</t>
         </is>
       </c>
     </row>
@@ -22691,19 +25060,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K21" s="106" t="inlineStr">
+      <c r="K21" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L21" s="111" t="inlineStr">
+      <c r="L21" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_10 | BLOCKED: Need editor open cURL + iframe selector</t>
         </is>
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:24 (0.00s)</t>
+          <t>2026-06-18 15:03:55 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -22750,19 +25119,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K22" s="106" t="inlineStr">
+      <c r="K22" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L22" s="111" t="inlineStr">
+      <c r="L22" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_11 | BLOCKED: Need editor input selector</t>
         </is>
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:24 (0.00s)</t>
+          <t>2026-06-18 15:03:55 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -22809,19 +25178,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K23" s="106" t="inlineStr">
+      <c r="K23" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L23" s="111" t="inlineStr">
+      <c r="L23" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_12 | BLOCKED: Need autosave network call signature</t>
         </is>
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:24 (0.00s)</t>
+          <t>2026-06-18 15:03:55 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -22868,19 +25237,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K24" s="106" t="inlineStr">
+      <c r="K24" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L24" s="111" t="inlineStr">
+      <c r="L24" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_13 | BLOCKED: Need Save button selector + cURL</t>
         </is>
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:24 (0.00s)</t>
+          <t>2026-06-18 15:03:55 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -22927,19 +25296,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K25" s="106" t="inlineStr">
+      <c r="K25" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L25" s="111" t="inlineStr">
+      <c r="L25" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_14 | BLOCKED: Multi-session test — requires two parallel browser contexts</t>
         </is>
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:24 (0.00s)</t>
+          <t>2026-06-18 15:03:55 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -22986,19 +25355,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K26" s="106" t="inlineStr">
+      <c r="K26" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L26" s="111" t="inlineStr">
+      <c r="L26" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_15 | BLOCKED: Need formatting toolbar selectors</t>
         </is>
       </c>
       <c r="M26" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:24 (0.00s)</t>
+          <t>2026-06-18 15:03:55 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23045,19 +25414,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K27" s="106" t="inlineStr">
+      <c r="K27" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L27" s="111" t="inlineStr">
+      <c r="L27" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_16 | BLOCKED: Need insert-image button selector + cURL</t>
         </is>
       </c>
       <c r="M27" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:24 (0.00s)</t>
+          <t>2026-06-18 15:03:55 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23104,19 +25473,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K28" s="106" t="inlineStr">
+      <c r="K28" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L28" s="111" t="inlineStr">
+      <c r="L28" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_17 | BLOCKED: Need Undo/Redo button selectors</t>
         </is>
       </c>
       <c r="M28" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:24 (0.00s)</t>
+          <t>2026-06-18 15:03:55 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23163,19 +25532,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K29" s="106" t="inlineStr">
+      <c r="K29" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L29" s="111" t="inlineStr">
+      <c r="L29" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_18 | BLOCKED: Need fullscreen button selector</t>
         </is>
       </c>
       <c r="M29" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:24 (0.00s)</t>
+          <t>2026-06-18 15:03:55 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23222,19 +25591,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K30" s="106" t="inlineStr">
+      <c r="K30" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L30" s="111" t="inlineStr">
+      <c r="L30" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_19 | BLOCKED: Need insert-table button selector</t>
         </is>
       </c>
       <c r="M30" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:24 (0.00s)</t>
+          <t>2026-06-18 15:03:55 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23281,19 +25650,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K31" s="106" t="inlineStr">
+      <c r="K31" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L31" s="111" t="inlineStr">
+      <c r="L31" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_20 | BLOCKED: Need header button selector</t>
         </is>
       </c>
       <c r="M31" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:24 (0.00s)</t>
+          <t>2026-06-18 15:03:55 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23340,19 +25709,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K32" s="106" t="inlineStr">
+      <c r="K32" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L32" s="111" t="inlineStr">
+      <c r="L32" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_21 | BLOCKED: Need footer button selector</t>
         </is>
       </c>
       <c r="M32" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:24 (0.00s)</t>
+          <t>2026-06-18 15:03:55 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23399,19 +25768,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K33" s="106" t="inlineStr">
+      <c r="K33" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L33" s="111" t="inlineStr">
+      <c r="L33" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_22 | BLOCKED: Need print button + verification approach</t>
         </is>
       </c>
       <c r="M33" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:24 (0.00s)</t>
+          <t>2026-06-18 15:03:55 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23458,19 +25827,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K34" s="106" t="inlineStr">
+      <c r="K34" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L34" s="111" t="inlineStr">
+      <c r="L34" s="123" t="inlineStr">
         <is>
           <t>Skipped: TC_Creation_23 | BLOCKED: Need editor copy/paste verification approach</t>
         </is>
       </c>
       <c r="M34" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:24 (0.00s)</t>
+          <t>2026-06-18 15:03:55 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -23828,19 +26197,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K12" s="104" t="inlineStr">
+      <c r="K12" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="105" t="inlineStr">
+      <c r="L12" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:59:48 (11.39s)</t>
+          <t>2026-06-18 15:11:15 (20.81s)</t>
         </is>
       </c>
     </row>
@@ -23887,19 +26256,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="105" t="inlineStr">
+      <c r="L13" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:59:53 (4.68s)</t>
+          <t>2026-06-18 15:11:24 (8.94s)</t>
         </is>
       </c>
     </row>
@@ -23946,19 +26315,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="105" t="inlineStr">
+      <c r="L14" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:00:08 (14.74s)</t>
+          <t>2026-06-18 15:12:49 (84.64s)</t>
         </is>
       </c>
     </row>
@@ -24005,19 +26374,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="105" t="inlineStr">
+      <c r="L15" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:00:19 (11.31s)</t>
+          <t>2026-06-18 15:13:00 (11.51s)</t>
         </is>
       </c>
     </row>
@@ -24060,19 +26429,19 @@
       </c>
       <c r="I16" s="73" t="n"/>
       <c r="J16" s="73" t="n"/>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="105" t="inlineStr">
+      <c r="L16" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:00:30 (11.28s)</t>
+          <t>2026-06-18 15:13:12 (11.38s)</t>
         </is>
       </c>
     </row>
@@ -24119,19 +26488,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K17" s="104" t="inlineStr">
+      <c r="K17" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L17" s="105" t="inlineStr">
+      <c r="L17" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:00:43 (13.08s)</t>
+          <t>2026-06-18 15:13:25 (13.15s)</t>
         </is>
       </c>
     </row>
@@ -24178,19 +26547,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K18" s="104" t="inlineStr">
+      <c r="K18" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L18" s="105" t="inlineStr">
+      <c r="L18" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:00:54 (11.15s)</t>
+          <t>2026-06-18 15:13:36 (11.32s)</t>
         </is>
       </c>
     </row>
@@ -24237,19 +26606,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K19" s="104" t="inlineStr">
+      <c r="K19" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L19" s="105" t="inlineStr">
+      <c r="L19" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:01:09 (14.13s)</t>
+          <t>2026-06-18 15:13:50 (14.10s)</t>
         </is>
       </c>
     </row>
@@ -24296,19 +26665,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K20" s="104" t="inlineStr">
+      <c r="K20" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L20" s="105" t="inlineStr">
+      <c r="L20" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:01:20 (11.27s)</t>
+          <t>2026-06-18 15:14:02 (11.49s)</t>
         </is>
       </c>
     </row>
@@ -24355,19 +26724,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K21" s="104" t="inlineStr">
+      <c r="K21" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L21" s="105" t="inlineStr">
+      <c r="L21" s="130" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request</t>
         </is>
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:01:20 (0.32s)</t>
+          <t>2026-06-18 15:14:02 (0.28s)</t>
         </is>
       </c>
     </row>
@@ -24414,19 +26783,19 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="K22" s="106" t="inlineStr">
+      <c r="K22" s="122" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L22" s="107" t="inlineStr">
+      <c r="L22" s="131" t="inlineStr">
         <is>
           <t>Skipped: TC_delete_11 | NOT TESTABLE in current env. 'Shared With Me' exposes only a 'Remove Access' action — there is no Delete button on shared files. A true test needs a real shared-file fixture (a second user shares a file with this account), which the test environment does not provide.</t>
         </is>
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 17:01:20 (0.00s)</t>
+          <t>2026-06-18 15:14:02 (0.00s)</t>
         </is>
       </c>
     </row>
@@ -24776,19 +27145,19 @@
         </is>
       </c>
       <c r="J12" s="11" t="n"/>
-      <c r="K12" s="104" t="inlineStr">
+      <c r="K12" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="105" t="inlineStr">
+      <c r="L12" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:53 (11.89s)</t>
+          <t>2026-06-18 15:04:19 (7.38s)</t>
         </is>
       </c>
     </row>
@@ -24835,19 +27204,19 @@
         </is>
       </c>
       <c r="J13" s="11" t="n"/>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="105" t="inlineStr">
+      <c r="L13" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:50:56 (2.31s)</t>
+          <t>2026-06-18 15:04:22 (2.16s)</t>
         </is>
       </c>
     </row>
@@ -24894,19 +27263,19 @@
         </is>
       </c>
       <c r="J14" s="11" t="n"/>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="105" t="inlineStr">
+      <c r="L14" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:51:09 (12.07s)</t>
+          <t>2026-06-18 15:04:30 (7.71s)</t>
         </is>
       </c>
     </row>
@@ -24953,19 +27322,19 @@
         </is>
       </c>
       <c r="J15" s="11" t="n"/>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="105" t="inlineStr">
+      <c r="L15" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:51:21 (11.22s)</t>
+          <t>2026-06-18 15:04:39 (7.69s)</t>
         </is>
       </c>
     </row>
@@ -25012,19 +27381,19 @@
         </is>
       </c>
       <c r="J16" s="11" t="n"/>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="105" t="inlineStr">
+      <c r="L16" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:51:34 (13.18s)</t>
+          <t>2026-06-18 15:04:50 (9.78s)</t>
         </is>
       </c>
     </row>
@@ -25071,19 +27440,19 @@
         </is>
       </c>
       <c r="J17" s="11" t="n"/>
-      <c r="K17" s="104" t="inlineStr">
+      <c r="K17" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L17" s="105" t="inlineStr">
+      <c r="L17" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:51:58 (23.71s)</t>
+          <t>2026-06-18 15:05:04 (13.21s)</t>
         </is>
       </c>
     </row>
@@ -25130,19 +27499,19 @@
         </is>
       </c>
       <c r="J18" s="11" t="n"/>
-      <c r="K18" s="104" t="inlineStr">
+      <c r="K18" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L18" s="105" t="inlineStr">
+      <c r="L18" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:52:19 (20.68s)</t>
+          <t>2026-06-18 15:05:18 (13.90s)</t>
         </is>
       </c>
     </row>
@@ -25189,19 +27558,19 @@
         </is>
       </c>
       <c r="J19" s="11" t="n"/>
-      <c r="K19" s="104" t="inlineStr">
+      <c r="K19" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L19" s="105" t="inlineStr">
+      <c r="L19" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:52:30 (11.33s)</t>
+          <t>2026-06-18 15:05:26 (7.80s)</t>
         </is>
       </c>
     </row>
@@ -25248,19 +27617,19 @@
         </is>
       </c>
       <c r="J20" s="11" t="n"/>
-      <c r="K20" s="106" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="L20" s="107" t="inlineStr">
-        <is>
-          <t>Skipped: [UI] Need &gt;=2 folders for the duplicate-name test</t>
+      <c r="K20" s="120" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L20" s="130" t="inlineStr">
+        <is>
+          <t>HTTP 409 Conflict</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:52:33 (1.78s)</t>
+          <t>2026-06-18 15:05:32 (5.30s)</t>
         </is>
       </c>
     </row>
@@ -25307,15 +27676,15 @@
         </is>
       </c>
       <c r="J21" s="11" t="n"/>
-      <c r="K21" s="104" t="inlineStr">
+      <c r="K21" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L21" s="105" t="inlineStr"/>
+      <c r="L21" s="130" t="inlineStr"/>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:52:56 (22.19s)</t>
+          <t>2026-06-18 15:05:51 (18.70s)</t>
         </is>
       </c>
     </row>
@@ -25362,15 +27731,15 @@
         </is>
       </c>
       <c r="J22" s="11" t="n"/>
-      <c r="K22" s="104" t="inlineStr">
+      <c r="K22" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L22" s="105" t="inlineStr"/>
+      <c r="L22" s="130" t="inlineStr"/>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:53:18 (22.23s)</t>
+          <t>2026-06-18 15:06:10 (18.90s)</t>
         </is>
       </c>
     </row>
@@ -25417,19 +27786,19 @@
         </is>
       </c>
       <c r="J23" s="11" t="n"/>
-      <c r="K23" s="104" t="inlineStr">
+      <c r="K23" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L23" s="105" t="inlineStr">
+      <c r="L23" s="130" t="inlineStr">
         <is>
           <t>HTTP 0</t>
         </is>
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:53:30 (12.15s)</t>
+          <t>2026-06-18 15:06:17 (7.44s)</t>
         </is>
       </c>
     </row>
@@ -25476,19 +27845,19 @@
         </is>
       </c>
       <c r="J24" s="11" t="n"/>
-      <c r="K24" s="104" t="inlineStr">
+      <c r="K24" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L24" s="105" t="inlineStr">
+      <c r="L24" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:53:45 (14.56s)</t>
+          <t>2026-06-18 15:06:28 (9.94s)</t>
         </is>
       </c>
     </row>
@@ -25535,19 +27904,19 @@
         </is>
       </c>
       <c r="J25" s="11" t="n"/>
-      <c r="K25" s="104" t="inlineStr">
+      <c r="K25" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L25" s="105" t="inlineStr">
+      <c r="L25" s="130" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M25" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:54:16 (30.18s)</t>
+          <t>2026-06-18 15:06:47 (17.76s)</t>
         </is>
       </c>
     </row>
@@ -25591,7 +27960,7 @@
         </is>
       </c>
       <c r="J29" s="77" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" ht="31" customHeight="1" s="29">
@@ -25607,7 +27976,7 @@
         </is>
       </c>
       <c r="J30" s="77" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" ht="31" customHeight="1" s="29">
@@ -25639,7 +28008,7 @@
         </is>
       </c>
       <c r="J32" s="77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" ht="31" customHeight="1" s="29">
@@ -25900,19 +28269,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K12" s="104" t="inlineStr">
+      <c r="K12" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="110" t="inlineStr">
+      <c r="L12" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M12" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:54:35 (0.41s)</t>
+          <t>2026-06-18 15:07:05 (0.33s)</t>
         </is>
       </c>
     </row>
@@ -25959,19 +28328,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="110" t="inlineStr">
+      <c r="L13" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M13" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:54:36 (0.30s)</t>
+          <t>2026-06-18 15:07:05 (0.26s)</t>
         </is>
       </c>
     </row>
@@ -26018,19 +28387,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K14" s="108" t="inlineStr">
+      <c r="K14" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L14" s="112" t="inlineStr">
+      <c r="L14" s="125" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request | AssertionError: [API] Expected 200, got 400</t>
         </is>
       </c>
       <c r="M14" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:54:36 (0.38s)</t>
+          <t>2026-06-18 15:07:06 (0.34s)</t>
         </is>
       </c>
     </row>
@@ -26077,19 +28446,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="110" t="inlineStr">
+      <c r="L15" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M15" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:54:36 (0.33s)</t>
+          <t>2026-06-18 15:07:06 (0.34s)</t>
         </is>
       </c>
     </row>
@@ -26136,19 +28505,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="110" t="inlineStr">
+      <c r="L16" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M16" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:54:39 (3.08s)</t>
+          <t>2026-06-18 15:07:09 (2.93s)</t>
         </is>
       </c>
     </row>
@@ -26195,19 +28564,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K17" s="104" t="inlineStr">
+      <c r="K17" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L17" s="110" t="inlineStr">
+      <c r="L17" s="121" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request</t>
         </is>
       </c>
       <c r="M17" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:54:40 (0.66s)</t>
+          <t>2026-06-18 15:07:10 (0.66s)</t>
         </is>
       </c>
     </row>
@@ -26254,19 +28623,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K18" s="104" t="inlineStr">
+      <c r="K18" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L18" s="110" t="inlineStr">
+      <c r="L18" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M18" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:54:44 (3.88s)</t>
+          <t>2026-06-18 15:07:13 (3.47s)</t>
         </is>
       </c>
     </row>
@@ -26313,19 +28682,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K19" s="104" t="inlineStr">
+      <c r="K19" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L19" s="110" t="inlineStr">
+      <c r="L19" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M19" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:54:50 (5.60s)</t>
+          <t>2026-06-18 15:07:18 (4.66s)</t>
         </is>
       </c>
     </row>
@@ -26372,19 +28741,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K20" s="104" t="inlineStr">
+      <c r="K20" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L20" s="110" t="inlineStr">
+      <c r="L20" s="121" t="inlineStr">
         <is>
           <t>HTTP 0</t>
         </is>
       </c>
       <c r="M20" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:54:56 (6.76s)</t>
+          <t>2026-06-18 15:07:24 (5.93s)</t>
         </is>
       </c>
     </row>
@@ -26431,19 +28800,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K21" s="104" t="inlineStr">
+      <c r="K21" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L21" s="110" t="inlineStr">
+      <c r="L21" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M21" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:55:02 (5.57s)</t>
+          <t>2026-06-18 15:07:29 (5.45s)</t>
         </is>
       </c>
     </row>
@@ -26490,19 +28859,19 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K22" s="104" t="inlineStr">
+      <c r="K22" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L22" s="110" t="inlineStr">
+      <c r="L22" s="121" t="inlineStr">
         <is>
           <t>HTTP 404 Not Found</t>
         </is>
       </c>
       <c r="M22" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:55:02 (0.16s)</t>
+          <t>2026-06-18 15:07:29 (0.20s)</t>
         </is>
       </c>
     </row>
@@ -26549,19 +28918,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K23" s="108" t="inlineStr">
+      <c r="K23" s="124" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L23" s="112" t="inlineStr">
+      <c r="L23" s="125" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request | AssertionError: [API] Bulk move failed: 400</t>
         </is>
       </c>
       <c r="M23" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:55:02 (0.31s)</t>
+          <t>2026-06-18 15:07:30 (0.32s)</t>
         </is>
       </c>
     </row>
@@ -26608,19 +28977,19 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K24" s="104" t="inlineStr">
+      <c r="K24" s="120" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L24" s="110" t="inlineStr">
+      <c r="L24" s="121" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
       </c>
       <c r="M24" s="74" t="inlineStr">
         <is>
-          <t>2026-06-11 16:55:05 (3.05s)</t>
+          <t>2026-06-18 15:07:33 (2.88s)</t>
         </is>
       </c>
     </row>
@@ -26799,7 +29168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="25" bestFit="1" customWidth="1" style="29" min="1" max="1"/>
@@ -27023,12 +29392,12 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K12" s="104" t="inlineStr">
+      <c r="K12" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L12" s="105" t="inlineStr">
+      <c r="L12" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
@@ -27082,12 +29451,12 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K13" s="104" t="inlineStr">
+      <c r="K13" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L13" s="105" t="inlineStr">
+      <c r="L13" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
@@ -27141,12 +29510,12 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K14" s="104" t="inlineStr">
+      <c r="K14" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L14" s="105" t="inlineStr">
+      <c r="L14" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
@@ -27200,12 +29569,12 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K15" s="104" t="inlineStr">
+      <c r="K15" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L15" s="105" t="inlineStr">
+      <c r="L15" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
@@ -27259,12 +29628,12 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K16" s="104" t="inlineStr">
+      <c r="K16" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L16" s="105" t="inlineStr">
+      <c r="L16" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
@@ -27318,12 +29687,12 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K17" s="104" t="inlineStr">
+      <c r="K17" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L17" s="105" t="inlineStr">
+      <c r="L17" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
@@ -27377,12 +29746,12 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K18" s="104" t="inlineStr">
+      <c r="K18" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L18" s="105" t="inlineStr"/>
+      <c r="L18" s="92" t="n"/>
       <c r="M18" s="74" t="inlineStr">
         <is>
           <t>2026-06-11 16:58:58 (0.77s)</t>
@@ -27432,12 +29801,12 @@
           <t>409 Conflict</t>
         </is>
       </c>
-      <c r="K19" s="104" t="inlineStr">
+      <c r="K19" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L19" s="105" t="inlineStr">
+      <c r="L19" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
@@ -27491,12 +29860,12 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K20" s="104" t="inlineStr">
+      <c r="K20" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L20" s="105" t="inlineStr">
+      <c r="L20" s="92" t="inlineStr">
         <is>
           <t>HTTP 404 Not Found</t>
         </is>
@@ -27550,12 +29919,12 @@
           <t>500 Internal Server Error</t>
         </is>
       </c>
-      <c r="K21" s="104" t="inlineStr">
+      <c r="K21" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L21" s="105" t="inlineStr">
+      <c r="L21" s="92" t="inlineStr">
         <is>
           <t>HTTP 500 Internal Server Error</t>
         </is>
@@ -27609,12 +29978,12 @@
           <t>408 Request Timeout</t>
         </is>
       </c>
-      <c r="K22" s="106" t="inlineStr">
+      <c r="K22" s="93" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L22" s="107" t="inlineStr">
+      <c r="L22" s="94" t="inlineStr">
         <is>
           <t>Skipped: Can't simulate true network failure deterministically</t>
         </is>
@@ -27668,12 +30037,12 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K23" s="104" t="inlineStr">
+      <c r="K23" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L23" s="105" t="inlineStr"/>
+      <c r="L23" s="92" t="n"/>
       <c r="M23" s="74" t="inlineStr">
         <is>
           <t>2026-06-11 16:59:07 (5.49s)</t>
@@ -27723,12 +30092,12 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K24" s="104" t="inlineStr">
+      <c r="K24" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L24" s="105" t="inlineStr"/>
+      <c r="L24" s="92" t="n"/>
       <c r="M24" s="74" t="inlineStr">
         <is>
           <t>2026-06-11 16:59:13 (6.08s)</t>
@@ -27778,12 +30147,12 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K25" s="104" t="inlineStr">
+      <c r="K25" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L25" s="105" t="inlineStr"/>
+      <c r="L25" s="92" t="n"/>
       <c r="M25" s="74" t="inlineStr">
         <is>
           <t>2026-06-11 16:59:19 (6.03s)</t>
@@ -27833,12 +30202,12 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K26" s="104" t="inlineStr">
+      <c r="K26" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L26" s="105" t="inlineStr">
+      <c r="L26" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
@@ -27892,12 +30261,12 @@
           <t>400 Bad Request</t>
         </is>
       </c>
-      <c r="K27" s="108" t="inlineStr">
+      <c r="K27" s="95" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="L27" s="109" t="inlineStr">
+      <c r="L27" s="96" t="inlineStr">
         <is>
           <t>HTTP 200 OK | AssertionError: [API] Expected 4xx/5xx for invalid file id, got 200</t>
         </is>
@@ -27951,12 +30320,12 @@
           <t>403 Forbidden</t>
         </is>
       </c>
-      <c r="K28" s="106" t="inlineStr">
+      <c r="K28" s="93" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L28" s="107" t="inlineStr">
+      <c r="L28" s="94" t="inlineStr">
         <is>
           <t>Skipped: Requires a second user (owner) and a clear unshare API</t>
         </is>
@@ -28010,12 +30379,12 @@
           <t>200 OK</t>
         </is>
       </c>
-      <c r="K29" s="104" t="inlineStr">
+      <c r="K29" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="L29" s="105" t="inlineStr">
+      <c r="L29" s="92" t="inlineStr">
         <is>
           <t>HTTP 200 OK</t>
         </is>
@@ -28069,12 +30438,12 @@
           <t>201 Created</t>
         </is>
       </c>
-      <c r="K30" s="106" t="inlineStr">
+      <c r="K30" s="93" t="inlineStr">
         <is>
           <t>Skipped</t>
         </is>
       </c>
-      <c r="L30" s="107" t="inlineStr">
+      <c r="L30" s="94" t="inlineStr">
         <is>
           <t>Skipped: Requires second + third user sessions to verify</t>
         </is>
@@ -28085,8 +30454,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33" ht="15.5" customHeight="1" s="29">
       <c r="A33" s="51" t="inlineStr">
         <is>
@@ -28193,10 +30560,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
